--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45938</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>45677</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>45153</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45541</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46101</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45404</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44103</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>46055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>44965</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>46053</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46181</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>46086</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>46091</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>46201</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>46216</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>46219</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45440</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45926</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>46031</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>46185</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>46201</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>46062</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46134</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45187</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46253</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45721</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45699</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44505</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>44744</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44515</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44799</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44829</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45252</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44949</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45730</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>44663</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45194</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>46045</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45891</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45177</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>46057</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>45899</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45089</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45926</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>45930</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>46148</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>45446</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45981</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44958</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>46168</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>46169</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>46021</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46030</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>46175</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>46059</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>46182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>46069</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>46182</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>46084</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>46188</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>46093</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>46097</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>46162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>46104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>46105</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>46114</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>46119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>46133</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>45453</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>44955</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>46261</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>46219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>46262</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>46262</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>46254</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>46269</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>46281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>46239</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>46239</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46239</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45800</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>45800</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>45868</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45883</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45064</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45706</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45699</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45706</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>44868</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>44774</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>44460</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>44510</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44501</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44760</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44873</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>44854</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44512</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>44876</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>44635</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>44596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44595</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>44501</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>44519</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44595</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>44861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44817</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44854</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44523</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44714</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>44635</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44603</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44817</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44672</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45022</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45488</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44510</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44656</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>44846</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44988</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44988</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45523</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45191</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45671</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45540</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45649</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45771</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45240</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45281</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45212</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45693</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45365</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>44994</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45701</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>45544</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>44477</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45191</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45638</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>44988</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45169</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44744</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45162</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45162</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45730</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45649</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45208</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45408</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45649</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45567</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45589</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45260</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45615</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45615</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>44813</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45226</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45251</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>44797</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45480</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>44582</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44804</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45667</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45252</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45240</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45540</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45112</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45884</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45887</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45905</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45709</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>46035</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>46030</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46080</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45467</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>46030</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45884</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45884</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>46134</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>46029</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44501</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45238</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>44549</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45701</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46061</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45161</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45121</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45769</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46037</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45390</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>46052</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>46063</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45252</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45706</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45330</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45660</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45562</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45887</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45670</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45888</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>46104</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>46136</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>46093</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45356</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45884</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>46046</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45891</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45246</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45478</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45769</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45558</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45120</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45602</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45896</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45735</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>46071</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>46136</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>46069</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45552</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45899</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>44586</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>46048</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45537</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45779</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>46048</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>46042</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45728</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>46044</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>46071</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46069</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>46065</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>45211</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>46063</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>46058</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>46058</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>46090</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>46065</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>46140</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45910</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>46055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45910</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>46063</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>46141</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45883</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>46085</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>46043</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>46031</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45070</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45636</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45087</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45916</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45530</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>46090</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45512</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>46030</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45919</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45919</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45460</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45153</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46038</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45925</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45925</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45261</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>44918</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45926</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45926</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>45576</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>46105</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45926</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>46142</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>46072</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45271</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45926</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44918</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45930</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>46065</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45245</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>45931</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45404</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45933</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45933</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45069</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45933</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45666</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>46147</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45755</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45936</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>46147</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>46147</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45415</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44994</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>44994</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>45936</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>46115</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>46147</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>46147</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>46038</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45414</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45649</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45938</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45939</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>45938</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45343</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>45937</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>45938</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>45943</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45945</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>46148</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>45930</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>45930</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>45945</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45946</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>45730</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45730</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45946</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>46151</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>46050</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45293</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>45293</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>46035</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45327</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>46150</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45957</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>46043</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>46153</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45321</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>45268</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>46108</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>46079</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>46048</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45153</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45971</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45971</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45968</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45971</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45975</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45196</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45977</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>46086</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45288</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46086</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>44797</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45978</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45645</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45979</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45226</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45701</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44544</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45162</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45983</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45984</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45984</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45984</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45981</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44988</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45209</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45981</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>46094</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45985</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>46104</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>45986</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>46108</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>45159</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46161</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44949</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45992</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45992</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45992</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>46107</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45992</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>46115</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45103</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>46034</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45722</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46163</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45617</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>46163</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>46030</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45666</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>46163</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>46163</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45999</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44972</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>46163</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45212</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>46165</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>46000</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>46000</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45984</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>45721</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>45721</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45721</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45986</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45999</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>45999</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>46000</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>46167</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>46165</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>46165</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>46165</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>46165</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45075</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>45483</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45984</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>46169</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>46169</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45182</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>46013</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44843</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>46168</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>46168</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>46169</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>46169</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45327</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>46169</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>46169</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>46128</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>46021</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44810</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45698</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45210</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45265</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>44586</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>46031</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>46031</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>45250</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>46034</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>46171</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>46035</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>46035</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>46037</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>46171</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>46036</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>46036</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>46045</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45112</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>46036</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>46036</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>46036</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>46038</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>46045</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>46043</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>46042</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>46043</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45274</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>46052</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>46044</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>46044</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>46045</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45758</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>46045</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45476</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>46050</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>46175</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>46175</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>46050</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>46176</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>46176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>46175</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>46051</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>46051</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>46055</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>46055</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>46178</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>46132</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>46178</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>46178</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>46178</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>46178</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>46055</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>46056</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45191</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>46069</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>46043</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>46056</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         <v>46178</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45376</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>46178</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>46178</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>46056</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>46058</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>46058</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>46058</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>46058</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>46058</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45075</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>46063</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>46063</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>46062</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>46063</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>46178</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>46063</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>46063</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>46063</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>46062</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>46063</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>46065</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45562</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>46177</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>46065</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>46177</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>46065</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>46064</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>46065</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45069</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>46069</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>46066</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>46069</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>46066</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>46066</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45075</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>44805</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>46071</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>46073</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>46073</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>46072</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>46072</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46282,7 +46282,7 @@
         <v>46072</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>46076</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45099</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>46184</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>46074</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>44908</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>46076</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45240</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>46031</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>46078</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>46034</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45639</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>46080</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>46184</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>46036</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>46080</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>46183</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46084</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46084</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>46084</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45320</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>46037</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46084</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>46086</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>46085</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>46086</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48225,7 +48225,7 @@
         <v>46086</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>46085</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>46086</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>46185</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>46085</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>46085</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>46086</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>46086</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>46086</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>46086</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>46185</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49058,7 +49058,7 @@
         <v>46086</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>46086</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46087</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>46185</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>46090</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>46087</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>46087</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>46090</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49667,7 +49667,7 @@
         <v>46185</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45374</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49813,7 +49813,7 @@
         <v>44854</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>46090</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>46092</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>46092</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>46091</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50198,7 +50198,7 @@
         <v>45205</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>46091</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>46092</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>46092</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>46043</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>46092</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50651,7 +50651,7 @@
         <v>46190</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>46091</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>46093</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50880,7 +50880,7 @@
         <v>45721</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>46190</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>46094</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51104,7 +51104,7 @@
         <v>46101</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45188</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45483</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>46093</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>46036</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>45226</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>46094</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>46097</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>46097</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>46095</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>44818</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>46034</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>46095</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>46095</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>46095</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>46095</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>46095</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>46098</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>46191</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46098</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>46095</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>46097</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
         <v>46195</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52813,7 +52813,7 @@
         <v>46099</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>46100</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52959,7 +52959,7 @@
         <v>46162</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>46100</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>46099</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>46196</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>46196</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>46099</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>46099</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>46196</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>46196</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>46099</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>44988</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>46196</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>46099</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>46101</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54031,7 +54031,7 @@
         <v>46101</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>46101</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54187,7 +54187,7 @@
         <v>44875</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>46058</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>46105</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>46106</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54484,7 +54484,7 @@
         <v>46198</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>46105</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54630,7 +54630,7 @@
         <v>46107</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>46107</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54786,7 +54786,7 @@
         <v>46107</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>46108</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>46108</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55015,7 +55015,7 @@
         <v>45112</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>46111</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>44796</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>46111</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>46111</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>46244</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>46201</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>46049</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45545</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>46112</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>46202</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>46114</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>46115</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55999,7 +55999,7 @@
         <v>46116</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56072,7 +56072,7 @@
         <v>46115</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>46115</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>46116</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>46115</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>46116</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>46115</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>46115</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56583,7 +56583,7 @@
         <v>45070</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>46119</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>46119</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56812,7 +56812,7 @@
         <v>46119</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56890,7 +56890,7 @@
         <v>46119</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56968,7 +56968,7 @@
         <v>46119</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>46119</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57124,7 +57124,7 @@
         <v>46120</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>44956</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>45300</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45282</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>46121</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>46121</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>46163</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57650,7 +57650,7 @@
         <v>46126</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>46126</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>46126</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>46126</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>46129</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>46129</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58098,7 +58098,7 @@
         <v>46129</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>46128</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>46128</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46129</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>46099</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>46129</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58556,7 +58556,7 @@
         <v>46129</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>46128</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>46128</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58780,7 +58780,7 @@
         <v>46107</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58853,7 +58853,7 @@
         <v>45602</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58926,7 +58926,7 @@
         <v>44901</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>46244</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
         <v>46244</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>46132</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59233,7 +59233,7 @@
         <v>46204</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>46204</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59389,7 +59389,7 @@
         <v>45252</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45082</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>46062</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59613,7 +59613,7 @@
         <v>46130</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>46132</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>46203</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59832,7 +59832,7 @@
         <v>45673</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>46204</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59978,7 +59978,7 @@
         <v>46091</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60056,7 +60056,7 @@
         <v>46132</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>46133</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>46132</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>46091</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>46135</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>46135</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>46086</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>46065</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60665,7 +60665,7 @@
         <v>46090</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60743,7 +60743,7 @@
         <v>45668</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60816,7 +60816,7 @@
         <v>46091</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>44914</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60967,7 +60967,7 @@
         <v>45476</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61040,7 +61040,7 @@
         <v>46204</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>46036</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>45257</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45303</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>46204</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61420,7 +61420,7 @@
         <v>45688</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61493,7 +61493,7 @@
         <v>44481</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61566,7 +61566,7 @@
         <v>46204</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>45595</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>45094</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61795,7 +61795,7 @@
         <v>46204</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61873,7 +61873,7 @@
         <v>46204</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61951,7 +61951,7 @@
         <v>44847</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62024,7 +62024,7 @@
         <v>46246</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>45049</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>46204</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>46247</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62326,7 +62326,7 @@
         <v>45264</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>46204</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62472,7 +62472,7 @@
         <v>46204</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62545,7 +62545,7 @@
         <v>45197</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>46251</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62696,7 +62696,7 @@
         <v>46251</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>46251</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>46160</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>46205</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>46205</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63076,7 +63076,7 @@
         <v>45217</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63149,7 +63149,7 @@
         <v>44564</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63222,7 +63222,7 @@
         <v>46244</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63295,7 +63295,7 @@
         <v>44551</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63373,7 +63373,7 @@
         <v>45561</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63446,7 +63446,7 @@
         <v>45063</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63524,7 +63524,7 @@
         <v>46252</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63597,7 +63597,7 @@
         <v>46253</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>45748</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63743,7 +63743,7 @@
         <v>46177</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63889,7 +63889,7 @@
         <v>45636</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>46255</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
         <v>45085</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>46255</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64186,7 +64186,7 @@
         <v>46258</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45701</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64337,7 +64337,7 @@
         <v>45700</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>46255</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64483,7 +64483,7 @@
         <v>44855</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64561,7 +64561,7 @@
         <v>44756</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64634,7 +64634,7 @@
         <v>45022</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64707,7 +64707,7 @@
         <v>46030</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64780,7 +64780,7 @@
         <v>46259</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64858,7 +64858,7 @@
         <v>46260</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64931,7 +64931,7 @@
         <v>45463</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>46261</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65082,7 +65082,7 @@
         <v>46261</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65160,7 +65160,7 @@
         <v>45541</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65238,7 +65238,7 @@
         <v>45541</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65316,7 +65316,7 @@
         <v>46261</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65394,7 +65394,7 @@
         <v>46261</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65472,7 +65472,7 @@
         <v>46261</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65550,7 +65550,7 @@
         <v>46261</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65628,7 +65628,7 @@
         <v>46261</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65701,7 +65701,7 @@
         <v>46261</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65774,7 +65774,7 @@
         <v>46261</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65847,7 +65847,7 @@
         <v>46261</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65920,7 +65920,7 @@
         <v>46261</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65998,7 +65998,7 @@
         <v>46261</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>46261</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66154,7 +66154,7 @@
         <v>46261</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>46261</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66310,7 +66310,7 @@
         <v>46262</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66388,7 +66388,7 @@
         <v>46262</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         <v>44587</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66539,7 +66539,7 @@
         <v>45327</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66612,7 +66612,7 @@
         <v>46262</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66690,7 +66690,7 @@
         <v>46262</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66768,7 +66768,7 @@
         <v>46219</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66841,7 +66841,7 @@
         <v>46262</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>46262</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>46262</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67075,7 +67075,7 @@
         <v>45769</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>46266</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67226,7 +67226,7 @@
         <v>46266</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>45590</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67377,7 +67377,7 @@
         <v>45672</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67450,7 +67450,7 @@
         <v>45211</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67523,7 +67523,7 @@
         <v>44566</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67596,7 +67596,7 @@
         <v>45153</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>45022</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>46000</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         <v>46230</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67898,7 +67898,7 @@
         <v>46230</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67976,7 +67976,7 @@
         <v>45779</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>46273</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68122,7 +68122,7 @@
         <v>45540</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68195,7 +68195,7 @@
         <v>46063</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68268,7 +68268,7 @@
         <v>46227</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68346,7 +68346,7 @@
         <v>45205</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68419,7 +68419,7 @@
         <v>45622</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68492,7 +68492,7 @@
         <v>45679</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68565,7 +68565,7 @@
         <v>45555</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68638,7 +68638,7 @@
         <v>46275</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68711,7 +68711,7 @@
         <v>45174</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68784,7 +68784,7 @@
         <v>44531</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68857,7 +68857,7 @@
         <v>46163</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68935,7 +68935,7 @@
         <v>45240</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69008,7 +69008,7 @@
         <v>45178</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69086,7 +69086,7 @@
         <v>45520</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69159,7 +69159,7 @@
         <v>46262</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69232,7 +69232,7 @@
         <v>45525</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69310,7 +69310,7 @@
         <v>46280</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69388,7 +69388,7 @@
         <v>46063</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69461,7 +69461,7 @@
         <v>45404</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69534,7 +69534,7 @@
         <v>45188</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69607,7 +69607,7 @@
         <v>45475</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69680,7 +69680,7 @@
         <v>45673</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69753,7 +69753,7 @@
         <v>45867</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69826,7 +69826,7 @@
         <v>45763</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69899,7 +69899,7 @@
         <v>45278</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69972,7 +69972,7 @@
         <v>45418</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70045,7 +70045,7 @@
         <v>45614</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70118,7 +70118,7 @@
         <v>45799</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70191,7 +70191,7 @@
         <v>45799</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70264,7 +70264,7 @@
         <v>45799</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70337,7 +70337,7 @@
         <v>46105</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70410,7 +70410,7 @@
         <v>45126</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70483,7 +70483,7 @@
         <v>45800</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70561,7 +70561,7 @@
         <v>45800</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70639,7 +70639,7 @@
         <v>45800</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70712,7 +70712,7 @@
         <v>45800</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>45805</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70868,7 +70868,7 @@
         <v>45810</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70946,7 +70946,7 @@
         <v>45819</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71019,7 +71019,7 @@
         <v>45819</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71092,7 +71092,7 @@
         <v>45819</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71165,7 +71165,7 @@
         <v>45825</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71238,7 +71238,7 @@
         <v>45827</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71311,7 +71311,7 @@
         <v>45833</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71384,7 +71384,7 @@
         <v>45832</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71462,7 +71462,7 @@
         <v>45831</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71535,7 +71535,7 @@
         <v>45840</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71613,7 +71613,7 @@
         <v>45845</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71691,7 +71691,7 @@
         <v>45762</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71764,7 +71764,7 @@
         <v>45842</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71837,7 +71837,7 @@
         <v>45863</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71910,7 +71910,7 @@
         <v>45866</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71988,7 +71988,7 @@
         <v>45866</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72066,7 +72066,7 @@
         <v>45867</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72139,7 +72139,7 @@
         <v>44784</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72212,7 +72212,7 @@
         <v>45870</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72290,7 +72290,7 @@
         <v>45873</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72363,7 +72363,7 @@
         <v>45873</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72436,7 +72436,7 @@
         <v>45873</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72509,7 +72509,7 @@
         <v>45873</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72582,7 +72582,7 @@
         <v>45883</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72655,7 +72655,7 @@
         <v>45883</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72728,7 +72728,7 @@
         <v>45883</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72801,7 +72801,7 @@
         <v>44102</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72879,7 +72879,7 @@
         <v>45316</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72957,7 +72957,7 @@
         <v>45315</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73035,7 +73035,7 @@
         <v>44484</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -73113,7 +73113,7 @@
         <v>45142</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -73191,7 +73191,7 @@
         <v>44550</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -73269,7 +73269,7 @@
         <v>45706</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -73347,7 +73347,7 @@
         <v>45720</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -73425,7 +73425,7 @@
         <v>45707</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -73503,7 +73503,7 @@
         <v>45707</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -73581,7 +73581,7 @@
         <v>46059</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73659,7 +73659,7 @@
         <v>46059</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73737,7 +73737,7 @@
         <v>46089</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73815,7 +73815,7 @@
         <v>46089</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>45084</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>45404</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45541</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>46101</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>45153</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44103</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>46053</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>46086</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46091</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>46055</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46201</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>46216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>46219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45566</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45926</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>46107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>46062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>46134</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>46031</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>46185</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>46188</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>46201</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45187</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>46251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>46261</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>44799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>46289</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45440</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>45699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44505</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44744</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>44829</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44955</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>46021</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>46030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45800</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>46059</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>46069</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45926</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45930</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>46084</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>46093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>46097</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>46105</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>46104</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>46114</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>46119</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>46133</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45981</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45177</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>46045</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45730</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>46057</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45899</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>46148</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>46168</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>46169</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44949</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>46175</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45868</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45252</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>46182</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>46182</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>46162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45453</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45883</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45194</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>46219</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>46262</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44663</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>46262</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>46261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>46254</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>46269</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>46281</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>46239</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>46239</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>46239</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45089</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45706</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45319</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45064</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45699</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45706</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>46122</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44868</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44774</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>44505</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44510</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>44501</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>44760</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44873</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>44854</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44512</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44876</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44635</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44595</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44501</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44519</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44595</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>44817</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44854</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44523</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44714</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44635</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44603</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44817</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44672</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45327</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45414</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45365</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45252</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45460</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45327</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45265</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45512</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>45226</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45467</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45281</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44914</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>46013</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45475</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>44854</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46021</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45883</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45188</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45404</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45274</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45483</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45300</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45418</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45278</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45883</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45884</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45884</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>45884</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45614</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45673</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>46031</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45763</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45800</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45800</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>46031</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45887</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>46034</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45800</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>46035</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45800</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>46036</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45552</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45888</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>46036</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>45330</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46036</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45887</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>46036</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>46035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>46035</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45540</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>44845</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>44564</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45799</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45070</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>46037</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>46042</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45769</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45891</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45896</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>44994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45069</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>46044</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45800</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>46043</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>46044</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45898</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44972</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>46043</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45721</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>46045</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45899</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45799</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46045</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>46050</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>44875</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46051</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46051</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45910</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45910</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>46050</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>46055</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>46055</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46043</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>46055</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46056</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>46056</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>46056</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>46058</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44587</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>46058</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>46062</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>46058</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>46058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>46058</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45916</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>46062</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46063</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45126</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>46063</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>46063</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46063</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>46063</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>46064</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46063</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>46065</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45919</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>46066</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>46066</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45919</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>46066</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46065</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46065</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>46065</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46069</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45099</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>46069</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45925</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>46072</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45926</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>46071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>46072</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45926</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45926</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>46072</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45925</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>46076</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46031</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>46074</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>46076</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46073</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46073</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>46034</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45930</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>46036</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>46078</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>46080</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45931</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>46080</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45805</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>46085</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>46084</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>46084</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>46085</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>46085</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>46037</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45810</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45252</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>46085</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45933</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>46084</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46084</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>46086</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>46087</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>46086</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>46086</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>46086</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44994</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>46087</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>46086</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>46086</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46087</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>46086</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>46086</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>46086</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>46086</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45933</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45933</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45936</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>46091</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>46090</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45937</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>46043</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>46090</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>45936</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>46091</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>45937</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>46091</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>46092</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>46093</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45938</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>46092</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>45938</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45590</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>46092</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>46093</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>46092</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>46092</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>46036</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45769</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>46094</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45390</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45938</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45939</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44477</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>46095</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>46095</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>46095</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>46095</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>46097</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>46097</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>46094</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46095</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>46097</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>46095</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>46095</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>46098</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45943</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>46099</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>46099</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>45930</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>45930</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>46099</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>46099</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>46098</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>45945</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>45946</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>46100</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44956</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>46100</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45217</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45946</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45945</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45082</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>46101</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>46101</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>45094</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>45182</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>46105</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>46107</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>46107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>46058</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>46106</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>46107</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>46111</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>44988</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>46108</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>46111</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>46111</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46108</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>46112</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>45261</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45957</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>46049</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45245</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>46115</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>46115</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>46115</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45478</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46115</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>46114</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>46115</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>46119</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>46119</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>46116</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>46116</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46119</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>46115</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>46116</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>46119</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>46119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>46119</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46163</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44797</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>46120</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>46121</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>46121</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46126</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45968</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46126</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46126</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46126</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46099</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45022</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45971</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45671</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>46130</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46132</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>46132</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45978</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>46129</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>46128</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>46132</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>46128</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>46128</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45975</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>46062</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>46091</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>45589</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>46132</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45977</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>46091</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46129</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>45979</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>46129</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46129</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>46129</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>46129</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>45602</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>46133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45981</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>46136</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45981</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>46091</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45986</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>46135</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45985</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45983</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45984</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45984</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>45984</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45615</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>46042</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         <v>46136</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>46135</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>46086</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>46093</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>46065</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>44582</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>45992</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>46090</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45558</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45992</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>45709</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45992</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45992</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45693</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>46048</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45730</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45356</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44481</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>46035</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45303</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45999</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>46065</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>46057</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45984</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45649</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45649</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45476</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>46063</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>46000</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45986</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45905</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45226</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45999</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45999</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>46000</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>46055</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>46000</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45735</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45188</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45779</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45819</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45984</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>46063</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46069</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45819</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>46065</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45819</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>46063</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>46071</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45670</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>46052</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45238</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44843</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>45562</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>46030</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45537</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>46104</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>46038</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45595</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45706</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45191</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>46044</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>46061</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45917</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>46046</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45728</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>46140</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45771</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>46058</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>46085</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>46080</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45211</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>46036</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45602</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>46069</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45825</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45883</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>46048</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46037</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46029</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>46134</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>46105</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45700</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>46030</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>46071</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>46043</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>46058</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>45257</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>46090</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>46090</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>46141</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>46072</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>46031</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45523</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45827</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45755</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>46038</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>45210</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>46065</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>44908</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45636</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46142</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45721</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45721</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>46148</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46147</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>46147</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46147</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>46147</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>46147</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>44847</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>46150</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45831</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>46043</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>46086</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>46048</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>46151</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>46086</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>46050</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>46079</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48577,7 +48577,7 @@
         <v>45833</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>46153</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>46035</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45649</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>46108</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>46094</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>46108</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>46104</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>44901</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>46115</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45561</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45840</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45049</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>44501</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45721</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>46161</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>45121</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>46034</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>46107</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44918</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>45842</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45845</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>46163</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>46163</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>46030</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>46163</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>45762</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46163</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>46163</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46163</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45701</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>44551</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>46165</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>44510</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>46165</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>46165</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>46167</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>46168</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>46165</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>46165</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>46168</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>46128</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>46169</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>46169</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>46169</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46169</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>46169</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>46052</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45545</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46171</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>46171</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>45866</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>46175</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>46175</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>46045</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>45863</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         <v>45866</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45867</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>46175</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>46045</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53155,7 +53155,7 @@
         <v>46177</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53228,7 +53228,7 @@
         <v>45483</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>46069</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>46132</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
         <v>45343</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>46177</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53598,7 +53598,7 @@
         <v>44988</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45112</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53744,7 +53744,7 @@
         <v>45870</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>46176</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>46176</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>45161</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45615</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>46178</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>46178</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>46178</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>46178</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>46178</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>46178</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45666</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>46178</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>46178</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>46178</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>44784</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45873</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>46183</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>46185</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>46185</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>46185</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46185</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45748</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>46184</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>46184</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>44855</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45873</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>45162</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45112</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45873</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45873</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>44586</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>46101</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45120</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>46190</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>46191</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>46034</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45758</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56593,7 +56593,7 @@
         <v>46190</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>46162</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>46195</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56822,7 +56822,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45639</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>46196</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>46196</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>46196</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>44549</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57280,7 +57280,7 @@
         <v>46196</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>46196</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>44813</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45541</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>45701</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>46201</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>44566</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>46198</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45075</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>46202</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45153</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>45153</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>46203</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>45112</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>45638</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>46204</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>45884</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>46204</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>46204</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>46204</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>46205</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>46204</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>46204</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>46204</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>46204</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>46204</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59223,7 +59223,7 @@
         <v>46205</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>45673</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>46251</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46251</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>46160</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>44810</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>46251</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>45212</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59832,7 +59832,7 @@
         <v>46252</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>45205</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59978,7 +59978,7 @@
         <v>45208</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>45211</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60124,7 +60124,7 @@
         <v>45666</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45698</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60270,7 +60270,7 @@
         <v>46177</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45209</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>46254</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>46253</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>45240</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>46255</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>46255</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60791,7 +60791,7 @@
         <v>46255</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         <v>45645</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60942,7 +60942,7 @@
         <v>46258</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61020,7 +61020,7 @@
         <v>45701</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45701</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61166,7 +61166,7 @@
         <v>46030</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61239,7 +61239,7 @@
         <v>45615</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>46259</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>45688</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61463,7 +61463,7 @@
         <v>45769</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>46260</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61609,7 +61609,7 @@
         <v>46262</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>46261</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>46261</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61843,7 +61843,7 @@
         <v>46262</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61916,7 +61916,7 @@
         <v>46261</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>46261</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>45250</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>46261</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>46261</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>46261</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62369,7 +62369,7 @@
         <v>46219</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62442,7 +62442,7 @@
         <v>46261</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62515,7 +62515,7 @@
         <v>46261</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62593,7 +62593,7 @@
         <v>45251</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>46262</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62744,7 +62744,7 @@
         <v>46262</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>46261</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62900,7 +62900,7 @@
         <v>45463</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62973,7 +62973,7 @@
         <v>46262</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63051,7 +63051,7 @@
         <v>46262</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63129,7 +63129,7 @@
         <v>46261</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63207,7 +63207,7 @@
         <v>46261</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>46262</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>46261</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>46261</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63514,7 +63514,7 @@
         <v>45226</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63587,7 +63587,7 @@
         <v>46261</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>44804</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>45408</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46266</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>46266</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63972,7 +63972,7 @@
         <v>44744</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>45246</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64118,7 +64118,7 @@
         <v>45321</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>46000</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45530</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64337,7 +64337,7 @@
         <v>45196</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>44796</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64488,7 +64488,7 @@
         <v>46227</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64566,7 +64566,7 @@
         <v>45240</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>44846</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64717,7 +64717,7 @@
         <v>45153</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>45488</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>46273</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64936,7 +64936,7 @@
         <v>46230</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65014,7 +65014,7 @@
         <v>46230</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>44586</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65165,7 +65165,7 @@
         <v>45282</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65238,7 +65238,7 @@
         <v>45264</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65311,7 +65311,7 @@
         <v>45265</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65384,7 +65384,7 @@
         <v>46275</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65457,7 +65457,7 @@
         <v>46063</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65530,7 +65530,7 @@
         <v>46280</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65608,7 +65608,7 @@
         <v>45293</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65681,7 +65681,7 @@
         <v>45293</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65754,7 +65754,7 @@
         <v>46163</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65832,7 +65832,7 @@
         <v>45660</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65905,7 +65905,7 @@
         <v>46262</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45540</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66051,7 +66051,7 @@
         <v>46204</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66129,7 +66129,7 @@
         <v>45260</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66202,7 +66202,7 @@
         <v>44544</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66275,7 +66275,7 @@
         <v>46063</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>44988</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66421,7 +66421,7 @@
         <v>44988</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66494,7 +66494,7 @@
         <v>46244</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66572,7 +66572,7 @@
         <v>45867</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66645,7 +66645,7 @@
         <v>46287</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66718,7 +66718,7 @@
         <v>46288</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>45022</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66869,7 +66869,7 @@
         <v>45374</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66942,7 +66942,7 @@
         <v>45376</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67015,7 +67015,7 @@
         <v>45562</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67088,7 +67088,7 @@
         <v>45271</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67166,7 +67166,7 @@
         <v>46288</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67239,7 +67239,7 @@
         <v>46287</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67312,7 +67312,7 @@
         <v>46244</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         <v>46244</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>45070</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67536,7 +67536,7 @@
         <v>45075</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67609,7 +67609,7 @@
         <v>46244</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>46287</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67765,7 +67765,7 @@
         <v>46247</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67843,7 +67843,7 @@
         <v>44805</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67916,7 +67916,7 @@
         <v>46246</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67994,7 +67994,7 @@
         <v>44656</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68067,7 +68067,7 @@
         <v>46105</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68140,7 +68140,7 @@
         <v>45404</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68218,7 +68218,7 @@
         <v>45075</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>45240</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68374,7 +68374,7 @@
         <v>44818</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68447,7 +68447,7 @@
         <v>45103</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68520,7 +68520,7 @@
         <v>45730</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68598,7 +68598,7 @@
         <v>45730</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68676,7 +68676,7 @@
         <v>45320</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68749,7 +68749,7 @@
         <v>45668</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68822,7 +68822,7 @@
         <v>45268</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68895,7 +68895,7 @@
         <v>45063</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68973,7 +68973,7 @@
         <v>45327</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69046,7 +69046,7 @@
         <v>44949</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69119,7 +69119,7 @@
         <v>45480</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69192,7 +69192,7 @@
         <v>45415</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69270,7 +69270,7 @@
         <v>45162</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69343,7 +69343,7 @@
         <v>45162</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69416,7 +69416,7 @@
         <v>45162</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69489,7 +69489,7 @@
         <v>45576</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69567,7 +69567,7 @@
         <v>45087</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69640,7 +69640,7 @@
         <v>45169</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69713,7 +69713,7 @@
         <v>45212</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69791,7 +69791,7 @@
         <v>45541</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69869,7 +69869,7 @@
         <v>44797</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69942,7 +69942,7 @@
         <v>44988</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70015,7 +70015,7 @@
         <v>45672</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70088,7 +70088,7 @@
         <v>45252</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70166,7 +70166,7 @@
         <v>45279</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70239,7 +70239,7 @@
         <v>45636</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70312,7 +70312,7 @@
         <v>45159</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70385,7 +70385,7 @@
         <v>45567</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70458,7 +70458,7 @@
         <v>45069</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70531,7 +70531,7 @@
         <v>45197</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70604,7 +70604,7 @@
         <v>45540</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70677,7 +70677,7 @@
         <v>44756</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70750,7 +70750,7 @@
         <v>45191</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70823,7 +70823,7 @@
         <v>44918</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70896,7 +70896,7 @@
         <v>45667</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70969,7 +70969,7 @@
         <v>45722</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>45476</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71120,7 +71120,7 @@
         <v>45022</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>45544</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71266,7 +71266,7 @@
         <v>45649</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71339,7 +71339,7 @@
         <v>45085</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71412,7 +71412,7 @@
         <v>45779</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71485,7 +71485,7 @@
         <v>45540</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71558,7 +71558,7 @@
         <v>45174</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71631,7 +71631,7 @@
         <v>45240</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71704,7 +71704,7 @@
         <v>45555</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71777,7 +71777,7 @@
         <v>45622</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71850,7 +71850,7 @@
         <v>45205</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71923,7 +71923,7 @@
         <v>45178</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72001,7 +72001,7 @@
         <v>44531</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72074,7 +72074,7 @@
         <v>45679</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72147,7 +72147,7 @@
         <v>45520</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72220,7 +72220,7 @@
         <v>45525</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72298,7 +72298,7 @@
         <v>44102</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72376,7 +72376,7 @@
         <v>44550</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72454,7 +72454,7 @@
         <v>45316</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72532,7 +72532,7 @@
         <v>45315</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72610,7 +72610,7 @@
         <v>45706</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72688,7 +72688,7 @@
         <v>44484</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72766,7 +72766,7 @@
         <v>45142</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72844,7 +72844,7 @@
         <v>45720</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72922,7 +72922,7 @@
         <v>45707</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -73000,7 +73000,7 @@
         <v>45707</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73078,7 +73078,7 @@
         <v>46059</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -73156,7 +73156,7 @@
         <v>46059</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -73234,7 +73234,7 @@
         <v>46089</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -73312,7 +73312,7 @@
         <v>46089</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>45084</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>45404</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45541</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>46101</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>45153</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44103</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>46053</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>46086</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46091</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>46055</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46201</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>46216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>46219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45566</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45926</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>46107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>46062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>46134</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>46031</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>46185</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>46188</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>46201</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45187</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>46251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>46261</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>44799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>46289</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45440</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>45699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44505</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44744</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>44829</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44955</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>46021</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>46030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45800</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>46059</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>46069</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45926</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45930</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>46084</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>46093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>46097</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>46105</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>46104</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>46114</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>46119</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>46133</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45981</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45177</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>46045</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45730</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>46057</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45899</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>46148</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>46168</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>46169</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44949</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>46175</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45868</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45252</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>46182</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>46182</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>46162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45453</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45883</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45194</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>46219</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>46262</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44663</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>46262</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>46261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>46254</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>46269</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>46281</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>46239</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>46239</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>46239</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45089</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45706</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45319</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45064</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45699</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45706</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>46122</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44868</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44774</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>44505</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44510</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>44501</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>44760</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44873</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>44854</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44512</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44876</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44635</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44595</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44501</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44519</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44595</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>44817</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44854</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44523</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44714</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44635</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44603</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44817</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44672</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45327</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45414</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45365</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45252</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45460</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45327</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45265</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45512</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>45226</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45467</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45281</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44914</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>46013</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45475</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>44854</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46021</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45883</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45188</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45404</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45274</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45483</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45300</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45418</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45278</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45883</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45884</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45884</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>45884</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45614</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45673</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>46031</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45763</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45800</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45800</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>46031</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45887</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>46034</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45800</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>46035</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45800</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>46036</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45552</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45888</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>46036</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>45330</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46036</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45887</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>46036</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>46035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>46035</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45540</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>44845</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>44564</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45799</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45070</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>46037</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>46042</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45769</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45891</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45896</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>44994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45069</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>46044</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45800</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>46043</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>46044</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45898</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44972</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>46043</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45721</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>46045</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45899</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45799</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46045</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>46050</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>44875</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46051</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46051</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45910</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45910</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>46050</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>46055</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>46055</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46043</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>46055</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46056</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>46056</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>46056</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>46058</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44587</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>46058</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>46062</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>46058</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>46058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>46058</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45916</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>46062</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46063</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45126</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>46063</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>46063</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46063</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>46063</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>46064</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46063</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>46065</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45919</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>46066</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>46066</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45919</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>46066</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46065</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46065</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>46065</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46069</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45099</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>46069</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45925</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>46072</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45926</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>46071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>46072</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45926</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45926</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>46072</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45925</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>46076</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46031</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>46074</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>46076</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46073</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46073</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>46034</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45930</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>46036</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>46078</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>46080</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45931</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>46080</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45805</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>46085</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>46084</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>46084</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>46085</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>46085</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>46037</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45810</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45252</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>46085</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45933</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>46084</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46084</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>46086</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>46087</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>46086</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>46086</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>46086</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44994</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>46087</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>46086</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>46086</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46087</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>46086</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>46086</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>46086</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>46086</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45933</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45933</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45936</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>46091</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>46090</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45937</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>46043</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>46090</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>45936</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>46091</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>45937</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>46091</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>46092</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>46093</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45938</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>46092</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>45938</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45590</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>46092</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>46093</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>46092</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>46092</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>46036</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45769</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>46094</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45390</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45938</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45939</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44477</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>46095</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>46095</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>46095</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>46095</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>46097</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>46097</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>46094</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46095</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>46097</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>46095</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>46095</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>46098</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45943</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>46099</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>46099</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>45930</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>45930</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>46099</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>46099</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>46098</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>45945</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>45946</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>46100</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44956</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>46100</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45217</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45946</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45945</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45082</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>46101</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>46101</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>45094</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>45182</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>46105</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>46107</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>46107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>46058</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>46106</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>46107</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>46111</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>44988</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>46108</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>46111</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>46111</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46108</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>46112</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>45261</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45957</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>46049</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45245</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>46115</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>46115</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>46115</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45478</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46115</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>46114</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>46115</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>46119</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>46119</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>46116</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>46116</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46119</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>46115</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>46116</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>46119</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>46119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>46119</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46163</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44797</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>46120</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>46121</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>46121</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46126</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45968</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46126</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46126</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46126</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46099</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45022</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45971</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45671</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>46130</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46132</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>46132</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45978</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>46129</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>46128</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>46132</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>46128</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>46128</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45975</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>46062</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>46091</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>45589</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>46132</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45977</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>46091</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46129</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>45979</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>46129</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46129</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>46129</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>46129</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>45602</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>46133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45981</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>46136</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45981</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>46091</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45986</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>46135</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45985</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45983</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45984</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45984</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>45984</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45615</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>46042</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         <v>46136</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>46135</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>46086</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>46093</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>46065</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>44582</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>45992</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>46090</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45558</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45992</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>45709</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45992</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45992</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45693</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>46048</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45730</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45356</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44481</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>46035</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45303</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45999</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>46065</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>46057</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45984</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45649</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45649</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45476</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>46063</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>46000</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45986</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45905</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45226</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45999</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45999</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>46000</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>46055</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>46000</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45735</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45188</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45779</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45819</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45984</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>46063</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46069</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45819</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>46065</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45819</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>46063</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>46071</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45670</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>46052</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45238</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44843</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>45562</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>46030</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45537</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>46104</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>46038</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45595</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45706</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45191</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>46044</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>46061</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45917</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>46046</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45728</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>46140</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45771</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>46058</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>46085</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>46080</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45211</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>46036</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45602</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>46069</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45825</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45883</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>46048</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46037</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46029</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>46134</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>46105</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45700</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>46030</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>46071</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>46043</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>46058</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>45257</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>46090</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>46090</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>46141</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>46072</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>46031</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45523</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45827</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45755</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>46038</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>45210</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>46065</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>44908</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45636</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46142</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45721</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45721</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>46148</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46147</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>46147</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46147</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>46147</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>46147</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>44847</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>46150</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45831</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>46043</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>46086</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>46048</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>46151</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>46086</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>46050</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>46079</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48577,7 +48577,7 @@
         <v>45833</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>46153</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>46035</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45649</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>46108</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>46094</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>46108</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>46104</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>44901</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>46115</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45561</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45840</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45049</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>44501</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45721</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>46161</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>45121</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>46034</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>46107</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44918</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>45842</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45845</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>46163</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>46163</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>46030</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>46163</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>45762</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46163</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>46163</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46163</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45701</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>44551</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>46165</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>44510</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>46165</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>46165</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>46167</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>46168</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>46165</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>46165</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>46168</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>46128</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>46169</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>46169</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>46169</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46169</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>46169</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>46052</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45545</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46171</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>46171</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>45866</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>46175</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>46175</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>46045</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>45863</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         <v>45866</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45867</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>46175</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>46045</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53155,7 +53155,7 @@
         <v>46177</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53228,7 +53228,7 @@
         <v>45483</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>46069</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>46132</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
         <v>45343</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>46177</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53598,7 +53598,7 @@
         <v>44988</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45112</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53744,7 +53744,7 @@
         <v>45870</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>46176</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>46176</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>45161</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45615</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>46178</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>46178</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>46178</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>46178</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>46178</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>46178</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45666</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>46178</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>46178</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>46178</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>44784</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45873</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>46183</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>46185</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>46185</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>46185</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46185</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45748</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>46184</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>46184</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>44855</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45873</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>45162</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45112</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45873</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45873</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>44586</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>46101</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45120</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>46190</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>46191</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>46034</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45758</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56593,7 +56593,7 @@
         <v>46190</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>46162</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>46195</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56822,7 +56822,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45639</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>46196</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>46196</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>46196</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>44549</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57280,7 +57280,7 @@
         <v>46196</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>46196</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>44813</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45541</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>45701</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>46201</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>44566</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>46198</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>45075</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>46202</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45153</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>45153</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>46203</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>45112</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>45638</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>46204</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>45884</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>46204</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>46204</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>46204</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>46205</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>46204</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>46204</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>46204</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>46204</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>46204</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59223,7 +59223,7 @@
         <v>46205</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>45673</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>46251</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46251</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>46160</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>44810</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>46251</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>45212</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59832,7 +59832,7 @@
         <v>46252</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>45205</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59978,7 +59978,7 @@
         <v>45208</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>45211</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60124,7 +60124,7 @@
         <v>45666</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45698</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60270,7 +60270,7 @@
         <v>46177</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45209</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>46254</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>46253</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>45240</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>46255</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>46255</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60791,7 +60791,7 @@
         <v>46255</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         <v>45645</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60942,7 +60942,7 @@
         <v>46258</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61020,7 +61020,7 @@
         <v>45701</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45701</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61166,7 +61166,7 @@
         <v>46030</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61239,7 +61239,7 @@
         <v>45615</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>46259</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>45688</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61463,7 +61463,7 @@
         <v>45769</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>46260</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61609,7 +61609,7 @@
         <v>46262</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>46261</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>46261</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61843,7 +61843,7 @@
         <v>46262</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61916,7 +61916,7 @@
         <v>46261</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>46261</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>45250</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>46261</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>46261</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>46261</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62369,7 +62369,7 @@
         <v>46219</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62442,7 +62442,7 @@
         <v>46261</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62515,7 +62515,7 @@
         <v>46261</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62593,7 +62593,7 @@
         <v>45251</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>46262</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62744,7 +62744,7 @@
         <v>46262</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>46261</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62900,7 +62900,7 @@
         <v>45463</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62973,7 +62973,7 @@
         <v>46262</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63051,7 +63051,7 @@
         <v>46262</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63129,7 +63129,7 @@
         <v>46261</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63207,7 +63207,7 @@
         <v>46261</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>46262</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>46261</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>46261</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63514,7 +63514,7 @@
         <v>45226</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63587,7 +63587,7 @@
         <v>46261</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>44804</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>45408</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46266</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>46266</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63972,7 +63972,7 @@
         <v>44744</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>45246</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64118,7 +64118,7 @@
         <v>45321</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>46000</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45530</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64337,7 +64337,7 @@
         <v>45196</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>44796</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64488,7 +64488,7 @@
         <v>46227</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64566,7 +64566,7 @@
         <v>45240</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>44846</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64717,7 +64717,7 @@
         <v>45153</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>45488</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>46273</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64936,7 +64936,7 @@
         <v>46230</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65014,7 +65014,7 @@
         <v>46230</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>44586</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65165,7 +65165,7 @@
         <v>45282</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65238,7 +65238,7 @@
         <v>45264</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65311,7 +65311,7 @@
         <v>45265</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65384,7 +65384,7 @@
         <v>46275</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65457,7 +65457,7 @@
         <v>46063</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65530,7 +65530,7 @@
         <v>46280</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65608,7 +65608,7 @@
         <v>45293</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65681,7 +65681,7 @@
         <v>45293</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65754,7 +65754,7 @@
         <v>46163</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65832,7 +65832,7 @@
         <v>45660</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65905,7 +65905,7 @@
         <v>46262</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45540</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66051,7 +66051,7 @@
         <v>46204</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66129,7 +66129,7 @@
         <v>45260</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66202,7 +66202,7 @@
         <v>44544</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66275,7 +66275,7 @@
         <v>46063</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>44988</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66421,7 +66421,7 @@
         <v>44988</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66494,7 +66494,7 @@
         <v>46244</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66572,7 +66572,7 @@
         <v>45867</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66645,7 +66645,7 @@
         <v>46287</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66718,7 +66718,7 @@
         <v>46288</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>45022</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66869,7 +66869,7 @@
         <v>45374</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66942,7 +66942,7 @@
         <v>45376</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67015,7 +67015,7 @@
         <v>45562</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67088,7 +67088,7 @@
         <v>45271</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67166,7 +67166,7 @@
         <v>46288</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67239,7 +67239,7 @@
         <v>46287</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67312,7 +67312,7 @@
         <v>46244</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         <v>46244</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>45070</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67536,7 +67536,7 @@
         <v>45075</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67609,7 +67609,7 @@
         <v>46244</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>46287</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67765,7 +67765,7 @@
         <v>46247</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67843,7 +67843,7 @@
         <v>44805</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67916,7 +67916,7 @@
         <v>46246</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67994,7 +67994,7 @@
         <v>44656</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68067,7 +68067,7 @@
         <v>46105</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68140,7 +68140,7 @@
         <v>45404</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68218,7 +68218,7 @@
         <v>45075</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>45240</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68374,7 +68374,7 @@
         <v>44818</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68447,7 +68447,7 @@
         <v>45103</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68520,7 +68520,7 @@
         <v>45730</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68598,7 +68598,7 @@
         <v>45730</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68676,7 +68676,7 @@
         <v>45320</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68749,7 +68749,7 @@
         <v>45668</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68822,7 +68822,7 @@
         <v>45268</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68895,7 +68895,7 @@
         <v>45063</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68973,7 +68973,7 @@
         <v>45327</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69046,7 +69046,7 @@
         <v>44949</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69119,7 +69119,7 @@
         <v>45480</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69192,7 +69192,7 @@
         <v>45415</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69270,7 +69270,7 @@
         <v>45162</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69343,7 +69343,7 @@
         <v>45162</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69416,7 +69416,7 @@
         <v>45162</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69489,7 +69489,7 @@
         <v>45576</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69567,7 +69567,7 @@
         <v>45087</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69640,7 +69640,7 @@
         <v>45169</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69713,7 +69713,7 @@
         <v>45212</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69791,7 +69791,7 @@
         <v>45541</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69869,7 +69869,7 @@
         <v>44797</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69942,7 +69942,7 @@
         <v>44988</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70015,7 +70015,7 @@
         <v>45672</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70088,7 +70088,7 @@
         <v>45252</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70166,7 +70166,7 @@
         <v>45279</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70239,7 +70239,7 @@
         <v>45636</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70312,7 +70312,7 @@
         <v>45159</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70385,7 +70385,7 @@
         <v>45567</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70458,7 +70458,7 @@
         <v>45069</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70531,7 +70531,7 @@
         <v>45197</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70604,7 +70604,7 @@
         <v>45540</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70677,7 +70677,7 @@
         <v>44756</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70750,7 +70750,7 @@
         <v>45191</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70823,7 +70823,7 @@
         <v>44918</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70896,7 +70896,7 @@
         <v>45667</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70969,7 +70969,7 @@
         <v>45722</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>45476</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71120,7 +71120,7 @@
         <v>45022</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>45544</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71266,7 +71266,7 @@
         <v>45649</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71339,7 +71339,7 @@
         <v>45085</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71412,7 +71412,7 @@
         <v>45779</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71485,7 +71485,7 @@
         <v>45540</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71558,7 +71558,7 @@
         <v>45174</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71631,7 +71631,7 @@
         <v>45240</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71704,7 +71704,7 @@
         <v>45555</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71777,7 +71777,7 @@
         <v>45622</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71850,7 +71850,7 @@
         <v>45205</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71923,7 +71923,7 @@
         <v>45178</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72001,7 +72001,7 @@
         <v>44531</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72074,7 +72074,7 @@
         <v>45679</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72147,7 +72147,7 @@
         <v>45520</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72220,7 +72220,7 @@
         <v>45525</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72298,7 +72298,7 @@
         <v>44102</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72376,7 +72376,7 @@
         <v>44550</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72454,7 +72454,7 @@
         <v>45316</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72532,7 +72532,7 @@
         <v>45315</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72610,7 +72610,7 @@
         <v>45706</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72688,7 +72688,7 @@
         <v>44484</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72766,7 +72766,7 @@
         <v>45142</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72844,7 +72844,7 @@
         <v>45720</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72922,7 +72922,7 @@
         <v>45707</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -73000,7 +73000,7 @@
         <v>45707</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73078,7 +73078,7 @@
         <v>46059</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -73156,7 +73156,7 @@
         <v>46059</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -73234,7 +73234,7 @@
         <v>46089</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -73312,7 +73312,7 @@
         <v>46089</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>45938</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>46101</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45677</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45541</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45404</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44103</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>46086</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>46091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>46055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46201</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>46216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>46219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>46053</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45926</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45440</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>46107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>46134</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>46031</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>46188</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>46201</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>46261</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45566</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>46289</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>46253</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45699</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44505</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44744</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>44829</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>45252</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>46021</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>46030</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>45800</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>46059</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45930</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>46069</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44949</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>46084</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>46093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>45730</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>44663</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>46097</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>46104</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45194</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>46105</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45981</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>46114</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>46119</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>46133</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>46045</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45089</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>45177</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>46057</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45899</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45868</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>46148</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>46168</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44958</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>46169</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45883</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>46175</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>46182</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>46182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>46188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45453</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>46261</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>46219</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>46262</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>46262</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>46269</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>46281</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>46239</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>46239</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>46239</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>46162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>46254</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44955</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45064</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45706</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45699</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45706</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44868</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44865</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44774</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44510</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44501</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44505</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44760</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44873</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44854</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44512</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44635</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44595</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44596</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44501</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44861</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44854</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44714</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44635</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44603</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44672</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45615</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45022</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44656</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44988</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>44846</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45191</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45523</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45671</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44845</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45281</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45520</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45212</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45525</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45265</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45540</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45649</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>45884</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>45771</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45887</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45540</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45240</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45800</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45884</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45884</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45693</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>46013</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45888</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>46021</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45891</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45365</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>46031</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46031</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45899</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44994</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>46034</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>46035</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45701</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44477</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>46035</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>46035</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>46037</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45191</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45638</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>46036</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46036</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46036</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>46036</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46036</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44988</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45404</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>46043</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>46042</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46043</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45910</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45169</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45188</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45475</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45910</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45673</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44744</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>46044</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>46044</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45763</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45278</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>46045</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>46045</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45418</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45614</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>46050</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45799</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45799</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45408</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45126</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45800</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45800</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>46050</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45800</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45800</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>46051</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45919</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45805</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>46051</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45919</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>46055</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45162</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45649</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46056</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45925</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45208</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45925</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>46043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>46056</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45926</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>46056</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45926</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>46058</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45926</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>46058</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>46058</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45730</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45926</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>46063</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>46063</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45649</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45930</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>46062</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46063</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>46063</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45931</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>46063</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46062</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46063</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46065</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>46065</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45933</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45933</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>46064</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46065</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45933</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>46069</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>46066</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46069</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45589</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45936</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>46066</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>46066</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>45937</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45936</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>46071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45938</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45939</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>45938</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45937</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45567</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>46073</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46073</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45260</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46072</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>46072</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46072</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45945</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45615</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>46076</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45615</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45930</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45930</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45945</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>46074</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46076</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45946</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45946</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45810</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46031</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44813</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46078</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46034</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46080</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45226</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>46036</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46080</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>46084</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>46084</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46084</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45480</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45251</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44797</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>46037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>46084</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>46086</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>46085</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>46086</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>46086</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46085</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>46086</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>46085</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>46085</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46086</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>46086</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>46086</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>46086</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>46086</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>46086</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>45957</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46087</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46090</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>46087</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>46087</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>46090</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>46092</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46092</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>46091</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>46091</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>46092</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>46092</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>46043</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>46092</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>46091</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>46093</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>44582</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46094</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44804</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45279</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>46093</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>46036</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>46094</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46097</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46097</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45971</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45971</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46095</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46095</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46095</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46095</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45968</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>46095</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>46095</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>46098</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>46095</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46097</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>46099</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>46100</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45971</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46100</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>46099</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>46099</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46099</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45112</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>46101</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45975</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>46101</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>45819</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45667</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45977</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>46106</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>45978</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>46105</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45979</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45252</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>46107</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>46107</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>46107</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>46108</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45540</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45240</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>46108</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>45819</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45983</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45984</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45984</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45984</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45819</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>46111</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>46111</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>46111</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45981</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45985</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>46112</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45986</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>46114</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>46115</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>46116</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>46115</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>46115</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>46116</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>46115</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>46116</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>46115</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>46115</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46119</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>46119</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>46119</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45825</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46119</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>46119</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>46119</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>46120</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45992</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45992</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45992</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46121</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45992</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>46121</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>46163</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>46126</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>46126</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>46126</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45827</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>46126</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45467</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>46129</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46129</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>46129</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>45999</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>46128</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>46129</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>46099</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>44501</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>46129</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>46129</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46128</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>46128</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46000</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46000</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44549</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45701</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>46132</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>45161</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>45986</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45121</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>45999</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45999</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45769</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>46062</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>46130</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>46132</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>46091</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>46132</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46133</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>46132</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>46091</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45390</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45833</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>46135</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45252</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>45706</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45660</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>46135</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45832</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>46086</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45670</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46065</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45831</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>46090</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>46091</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45246</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45478</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>45120</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45476</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>46036</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45840</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>44481</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>45595</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45905</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45709</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45845</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>44586</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45762</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>46080</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45842</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42902,7 +42902,7 @@
         <v>46030</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>46134</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>46029</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45211</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45238</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>46061</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>46037</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45070</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45636</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>46052</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>46063</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45087</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45562</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45530</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>46104</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>46136</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45512</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>46093</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45356</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>46046</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45460</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45558</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45153</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45602</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45735</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>46071</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>46136</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>46069</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45917</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>45261</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44918</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>46048</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45537</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45779</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>46048</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45576</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>46042</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45728</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>46057</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45271</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>46044</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>44918</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45245</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45404</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>46071</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>46069</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>46065</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>46063</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>46058</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>46058</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>46090</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>46065</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>46140</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>45069</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45666</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45863</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>46055</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45755</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>46063</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45866</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45866</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45415</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>46141</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>44994</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>44994</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45414</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45649</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45343</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45867</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45883</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>46085</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>46043</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>46031</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44784</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>46090</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48442,7 +48442,7 @@
         <v>46030</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48515,7 +48515,7 @@
         <v>46038</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45730</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45730</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45870</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>46105</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>46142</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>46072</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45873</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         <v>46065</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45261</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49260,7 +49260,7 @@
         <v>46147</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45293</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45293</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>46147</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>46147</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>46147</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>46147</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>46038</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45327</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>46148</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>45873</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45873</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45873</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>46151</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>46050</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50380,7 +50380,7 @@
         <v>46035</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>46150</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>46043</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>46153</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45321</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>46108</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45268</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>46079</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>46048</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>46086</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>46086</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>46094</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51271,7 +51271,7 @@
         <v>46104</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45153</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51417,7 +51417,7 @@
         <v>46108</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>46161</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>46107</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>46115</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>46034</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>45196</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51860,7 +51860,7 @@
         <v>46163</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>46163</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>46163</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>46030</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>46163</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>45288</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>44797</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52386,7 +52386,7 @@
         <v>46163</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45645</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>46163</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52620,7 +52620,7 @@
         <v>46165</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45226</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45701</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52849,7 +52849,7 @@
         <v>46167</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52922,7 +52922,7 @@
         <v>46165</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53000,7 +53000,7 @@
         <v>46165</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>46165</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>46165</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>44544</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45162</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>44988</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46169</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>46169</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45209</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46168</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>46168</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
         <v>46169</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>46169</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>46169</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>46169</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>46128</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45159</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>46171</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>44949</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>46171</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>46045</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>46045</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45883</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>46052</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45883</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>45883</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45103</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>46175</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>46175</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>46176</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>46176</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>46175</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>46178</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>46132</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>46178</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>46178</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55698,7 +55698,7 @@
         <v>45330</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>46178</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45887</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46069</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45884</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>46178</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>46178</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>45722</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56302,7 +56302,7 @@
         <v>46177</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>46177</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>45666</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56521,7 +56521,7 @@
         <v>46184</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>46184</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>44972</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56740,7 +56740,7 @@
         <v>45212</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>46183</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56896,7 +56896,7 @@
         <v>46185</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>46185</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>46185</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45721</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57193,7 +57193,7 @@
         <v>45721</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45721</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>46185</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57422,7 +57422,7 @@
         <v>46190</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         <v>45075</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>46101</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57651,7 +57651,7 @@
         <v>45483</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57724,7 +57724,7 @@
         <v>46034</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>46191</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>46195</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>46196</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58021,7 +58021,7 @@
         <v>46196</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>46196</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46196</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>45182</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58328,7 +58328,7 @@
         <v>44843</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58401,7 +58401,7 @@
         <v>46198</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45327</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
         <v>46201</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>46202</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58698,7 +58698,7 @@
         <v>44810</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>45698</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>45210</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58917,7 +58917,7 @@
         <v>46204</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>46204</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>46203</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>46204</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>45265</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>46204</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59370,7 +59370,7 @@
         <v>44586</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>46204</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59521,7 +59521,7 @@
         <v>46204</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59594,7 +59594,7 @@
         <v>46204</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59667,7 +59667,7 @@
         <v>45250</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59740,7 +59740,7 @@
         <v>46204</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>46160</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>46205</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>46205</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60037,7 +60037,7 @@
         <v>45112</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>46177</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60183,7 +60183,7 @@
         <v>45274</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45758</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60334,7 +60334,7 @@
         <v>46258</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60412,7 +60412,7 @@
         <v>45476</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60490,7 +60490,7 @@
         <v>46030</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60563,7 +60563,7 @@
         <v>46259</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60641,7 +60641,7 @@
         <v>46260</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60714,7 +60714,7 @@
         <v>46261</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60792,7 +60792,7 @@
         <v>46261</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>46261</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60948,7 +60948,7 @@
         <v>46261</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>46261</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>46261</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>46261</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61255,7 +61255,7 @@
         <v>46261</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61328,7 +61328,7 @@
         <v>46261</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>46261</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61474,7 +61474,7 @@
         <v>46261</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>46261</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>46261</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>46261</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61786,7 +61786,7 @@
         <v>46261</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>46262</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61942,7 +61942,7 @@
         <v>45191</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         <v>46262</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62088,7 +62088,7 @@
         <v>45376</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62161,7 +62161,7 @@
         <v>46262</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>46262</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62317,7 +62317,7 @@
         <v>46219</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>46262</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62468,7 +62468,7 @@
         <v>45075</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62546,7 +62546,7 @@
         <v>46262</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62624,7 +62624,7 @@
         <v>46262</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62702,7 +62702,7 @@
         <v>46266</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>46266</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62858,7 +62858,7 @@
         <v>45562</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62931,7 +62931,7 @@
         <v>45069</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63004,7 +63004,7 @@
         <v>45075</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63077,7 +63077,7 @@
         <v>44805</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63150,7 +63150,7 @@
         <v>46000</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>46230</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45099</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>46230</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63452,7 +63452,7 @@
         <v>44908</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63525,7 +63525,7 @@
         <v>46273</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63598,7 +63598,7 @@
         <v>45639</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>46227</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>45320</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63822,7 +63822,7 @@
         <v>46275</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63895,7 +63895,7 @@
         <v>46163</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63973,7 +63973,7 @@
         <v>46280</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64051,7 +64051,7 @@
         <v>46063</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>45374</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64197,7 +64197,7 @@
         <v>44854</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64270,7 +64270,7 @@
         <v>45205</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64343,7 +64343,7 @@
         <v>45721</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64421,7 +64421,7 @@
         <v>45188</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64499,7 +64499,7 @@
         <v>45483</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64572,7 +64572,7 @@
         <v>45867</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64645,7 +64645,7 @@
         <v>45226</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64718,7 +64718,7 @@
         <v>44818</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64791,7 +64791,7 @@
         <v>44988</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64864,7 +64864,7 @@
         <v>46287</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64937,7 +64937,7 @@
         <v>44875</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>46244</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65083,7 +65083,7 @@
         <v>46204</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65161,7 +65161,7 @@
         <v>46287</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65239,7 +65239,7 @@
         <v>46063</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65312,7 +65312,7 @@
         <v>46287</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65385,7 +65385,7 @@
         <v>45112</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65458,7 +65458,7 @@
         <v>46244</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65536,7 +65536,7 @@
         <v>44796</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65614,7 +65614,7 @@
         <v>46288</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>46288</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65760,7 +65760,7 @@
         <v>45545</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65838,7 +65838,7 @@
         <v>45070</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65911,7 +65911,7 @@
         <v>46246</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>44956</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66062,7 +66062,7 @@
         <v>45300</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         <v>45282</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66208,7 +66208,7 @@
         <v>45602</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>44901</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66354,7 +66354,7 @@
         <v>46247</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66432,7 +66432,7 @@
         <v>45252</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66510,7 +66510,7 @@
         <v>46105</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66583,7 +66583,7 @@
         <v>45082</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66656,7 +66656,7 @@
         <v>45673</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>46252</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>45668</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66875,7 +66875,7 @@
         <v>44914</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>46196</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>46190</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>46035</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67177,7 +67177,7 @@
         <v>45257</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67255,7 +67255,7 @@
         <v>46251</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67333,7 +67333,7 @@
         <v>45688</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67406,7 +67406,7 @@
         <v>46162</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67484,7 +67484,7 @@
         <v>45094</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67562,7 +67562,7 @@
         <v>46244</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67640,7 +67640,7 @@
         <v>46253</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67713,7 +67713,7 @@
         <v>44847</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67786,7 +67786,7 @@
         <v>46049</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>45049</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67932,7 +67932,7 @@
         <v>45264</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>46000</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68078,7 +68078,7 @@
         <v>46255</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68156,7 +68156,7 @@
         <v>46255</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68229,7 +68229,7 @@
         <v>45197</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68302,7 +68302,7 @@
         <v>45984</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68380,7 +68380,7 @@
         <v>46058</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>46058</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>46178</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68604,7 +68604,7 @@
         <v>46254</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68677,7 +68677,7 @@
         <v>46058</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68750,7 +68750,7 @@
         <v>46251</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68828,7 +68828,7 @@
         <v>46065</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68901,7 +68901,7 @@
         <v>46178</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68979,7 +68979,7 @@
         <v>46255</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69052,7 +69052,7 @@
         <v>46244</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69130,7 +69130,7 @@
         <v>46251</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69208,7 +69208,7 @@
         <v>45984</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69286,7 +69286,7 @@
         <v>46262</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69359,7 +69359,7 @@
         <v>46204</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69437,7 +69437,7 @@
         <v>45217</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69510,7 +69510,7 @@
         <v>44564</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69583,7 +69583,7 @@
         <v>44551</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69661,7 +69661,7 @@
         <v>45561</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69734,7 +69734,7 @@
         <v>45063</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69812,7 +69812,7 @@
         <v>45748</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69885,7 +69885,7 @@
         <v>45636</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69958,7 +69958,7 @@
         <v>45085</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70031,7 +70031,7 @@
         <v>45701</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70104,7 +70104,7 @@
         <v>45700</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70177,7 +70177,7 @@
         <v>44855</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70255,7 +70255,7 @@
         <v>44756</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70328,7 +70328,7 @@
         <v>45022</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70401,7 +70401,7 @@
         <v>45463</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70474,7 +70474,7 @@
         <v>45541</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70552,7 +70552,7 @@
         <v>45541</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70630,7 +70630,7 @@
         <v>44587</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70708,7 +70708,7 @@
         <v>45327</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70781,7 +70781,7 @@
         <v>45769</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70854,7 +70854,7 @@
         <v>45590</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70927,7 +70927,7 @@
         <v>45672</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71000,7 +71000,7 @@
         <v>45211</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71073,7 +71073,7 @@
         <v>44566</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71146,7 +71146,7 @@
         <v>45153</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71219,7 +71219,7 @@
         <v>45022</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71297,7 +71297,7 @@
         <v>45779</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71370,7 +71370,7 @@
         <v>45540</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71443,7 +71443,7 @@
         <v>45205</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71516,7 +71516,7 @@
         <v>45622</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71589,7 +71589,7 @@
         <v>45679</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71662,7 +71662,7 @@
         <v>45555</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71735,7 +71735,7 @@
         <v>45174</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71808,7 +71808,7 @@
         <v>44531</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71881,7 +71881,7 @@
         <v>45240</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71954,7 +71954,7 @@
         <v>45178</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72032,7 +72032,7 @@
         <v>44102</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72110,7 +72110,7 @@
         <v>45316</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72188,7 +72188,7 @@
         <v>45315</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72266,7 +72266,7 @@
         <v>44484</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72344,7 +72344,7 @@
         <v>45142</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72422,7 +72422,7 @@
         <v>44550</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72500,7 +72500,7 @@
         <v>45706</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72578,7 +72578,7 @@
         <v>45720</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72656,7 +72656,7 @@
         <v>45707</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72734,7 +72734,7 @@
         <v>45707</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72812,7 +72812,7 @@
         <v>46059</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72890,7 +72890,7 @@
         <v>46059</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72968,7 +72968,7 @@
         <v>46089</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73046,7 +73046,7 @@
         <v>46089</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>45938</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>46101</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45677</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45541</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45404</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44103</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>46086</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>46091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>46055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46201</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>46216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>46219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>46053</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45926</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45440</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>46107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>46134</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>46031</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>46188</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>46201</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>46261</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45566</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>46289</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>46253</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45699</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44505</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44744</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>44829</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>45252</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>46021</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>46030</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>45800</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>46059</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45930</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>46069</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44949</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>46084</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>46093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>45730</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>44663</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>46097</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>46104</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45194</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>46105</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45981</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>46114</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>46119</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>46133</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>46045</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45089</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>45177</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>46057</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45899</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45868</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>46148</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>46168</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44958</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>46169</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45883</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>46175</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>46182</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>46182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>46188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45453</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>46261</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>46219</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>46262</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>46262</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>46269</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>46281</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>46239</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>46239</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>46239</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>46162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>46254</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44955</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45064</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45706</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45699</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45706</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44868</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44865</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44774</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44510</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44501</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44505</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44760</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44873</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44854</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44512</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44635</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44595</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44596</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44501</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44861</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44854</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44714</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44635</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44603</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44672</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45615</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45022</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44656</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44988</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>44846</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45191</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45523</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45671</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44845</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45281</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45520</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45212</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45525</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45265</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45540</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45649</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>45884</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>45771</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45887</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45540</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45240</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45800</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45884</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45884</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45693</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>46013</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45888</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>46021</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45891</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45365</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>46031</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46031</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45899</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44994</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>46034</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>46035</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45701</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44477</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>46035</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>46035</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>46037</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45191</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45638</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>46036</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46036</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46036</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>46036</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46036</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44988</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45404</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>46043</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>46042</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46043</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45910</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45169</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45188</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45475</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45910</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45673</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44744</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>46044</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>46044</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45763</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45278</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>46045</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>46045</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45418</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45614</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>46050</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45799</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45799</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45408</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45126</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45800</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45800</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>46050</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45800</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45800</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>46051</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45919</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45805</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>46051</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45919</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>46055</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45162</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45649</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46056</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45925</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45208</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45925</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>46043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>46056</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45926</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>46056</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45926</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>46058</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45926</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>46058</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>46058</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45730</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45926</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>46063</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>46063</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45649</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45930</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>46062</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46063</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>46063</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45931</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>46063</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46062</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46063</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46065</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>46065</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45933</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45933</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>46064</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46065</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45933</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>46069</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>46066</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46069</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45589</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45936</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>46066</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>46066</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>45937</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45936</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>46071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45938</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45939</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>45938</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45937</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45567</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>46073</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46073</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45260</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46072</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>46072</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46072</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45945</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45615</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>46076</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45615</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45930</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45930</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45945</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>46074</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46076</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45946</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45946</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45810</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46031</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44813</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46078</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46034</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46080</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45226</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>46036</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46080</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>46084</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>46084</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46084</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45480</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45251</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44797</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>46037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>46084</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>46086</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>46085</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>46086</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>46086</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46085</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>46086</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>46085</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>46085</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46086</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>46086</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>46086</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>46086</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>46086</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>46086</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>45957</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46087</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46090</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>46087</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>46087</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>46090</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>46092</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46092</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>46091</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>46091</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>46092</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>46092</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>46043</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>46092</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>46091</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>46093</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>44582</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46094</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44804</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45279</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>46093</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>46036</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>46094</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46097</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46097</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45971</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45971</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46095</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46095</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46095</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46095</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45968</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>46095</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>46095</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>46098</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>46095</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46097</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>46099</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>46100</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45971</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46100</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>46099</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>46099</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46099</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45112</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>46101</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45975</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>46101</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>45819</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45667</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45977</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>46106</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>45978</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>46105</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45979</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45252</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>46107</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>46107</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>46107</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>46108</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45540</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45240</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>46108</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>45819</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45983</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45984</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45984</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45984</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45819</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>46111</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>46111</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>46111</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45981</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45985</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>46112</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45986</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>46114</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>46115</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>46116</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>46115</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>46115</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>46116</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>46115</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>46116</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>46115</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>46115</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46119</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>46119</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>46119</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45825</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46119</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>46119</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>46119</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>46120</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45992</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45992</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45992</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46121</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45992</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>46121</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>46163</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>46126</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>46126</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>46126</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45827</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>46126</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45467</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>46129</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46129</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>46129</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>45999</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>46128</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>46129</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>46099</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>44501</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>46129</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>46129</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46128</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>46128</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46000</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46000</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44549</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45701</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>46132</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>45161</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>45986</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45121</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>45999</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45999</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45769</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>46062</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>46130</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>46132</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>46091</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>46132</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46133</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>46132</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>46091</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45390</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45833</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>46135</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45252</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>45706</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45660</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>46135</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45832</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>46086</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45670</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46065</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45831</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>46090</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>46091</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45246</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45478</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>45120</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45476</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>46036</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45840</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>44481</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>45595</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45905</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45709</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45845</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>44586</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45762</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>46080</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45842</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42902,7 +42902,7 @@
         <v>46030</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>46134</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>46029</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45211</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45238</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>46061</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>46037</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45070</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45636</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>46052</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>46063</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45087</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45562</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45530</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>46104</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>46136</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45512</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>46093</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45356</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>46046</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45460</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45558</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45153</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45602</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45735</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>46071</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>46136</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>46069</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45917</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>45261</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44918</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>46048</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45537</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45779</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>46048</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45576</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>46042</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45728</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>46057</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45271</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>46044</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>44918</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45245</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45404</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>46071</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>46069</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>46065</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>46063</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>46058</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>46058</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>46090</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>46065</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>46140</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>45069</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45666</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45863</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>46055</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45755</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>46063</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45866</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45866</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45415</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>46141</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>44994</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>44994</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45414</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45649</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45343</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45867</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45883</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>46085</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>46043</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>46031</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44784</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>46090</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48442,7 +48442,7 @@
         <v>46030</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48515,7 +48515,7 @@
         <v>46038</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45730</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45730</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45870</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>46105</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>46142</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>46072</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45873</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         <v>46065</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45261</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49260,7 +49260,7 @@
         <v>46147</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45293</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45293</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>46147</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>46147</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>46147</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>46147</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>46038</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45327</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>46148</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>45873</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45873</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45873</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>46151</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>46050</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50380,7 +50380,7 @@
         <v>46035</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>46150</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>46043</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>46153</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45321</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>46108</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45268</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>46079</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>46048</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>46086</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>46086</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>46094</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51271,7 +51271,7 @@
         <v>46104</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45153</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51417,7 +51417,7 @@
         <v>46108</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>46161</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>46107</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>46115</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>46034</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>45196</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51860,7 +51860,7 @@
         <v>46163</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>46163</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>46163</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>46030</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>46163</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>45288</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>44797</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52386,7 +52386,7 @@
         <v>46163</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45645</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>46163</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52620,7 +52620,7 @@
         <v>46165</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45226</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45701</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52849,7 +52849,7 @@
         <v>46167</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52922,7 +52922,7 @@
         <v>46165</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53000,7 +53000,7 @@
         <v>46165</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>46165</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>46165</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>44544</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45162</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>44988</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46169</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>46169</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45209</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46168</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>46168</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
         <v>46169</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>46169</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>46169</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>46169</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>46128</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45159</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>46171</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>44949</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>46171</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>46045</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>46045</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45883</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>46052</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45883</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>45883</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45103</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>46175</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>46175</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>46176</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>46176</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>46175</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>46178</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>46132</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>46178</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>46178</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55698,7 +55698,7 @@
         <v>45330</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>46178</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45887</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46069</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45884</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>46178</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>46178</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>45722</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56302,7 +56302,7 @@
         <v>46177</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>46177</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>45666</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56521,7 +56521,7 @@
         <v>46184</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>46184</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>44972</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56740,7 +56740,7 @@
         <v>45212</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>46183</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56896,7 +56896,7 @@
         <v>46185</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>46185</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>46185</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45721</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57193,7 +57193,7 @@
         <v>45721</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45721</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>46185</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57422,7 +57422,7 @@
         <v>46190</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         <v>45075</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>46101</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57651,7 +57651,7 @@
         <v>45483</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57724,7 +57724,7 @@
         <v>46034</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>46191</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>46195</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>46196</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58021,7 +58021,7 @@
         <v>46196</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>46196</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46196</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>45182</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58328,7 +58328,7 @@
         <v>44843</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58401,7 +58401,7 @@
         <v>46198</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45327</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
         <v>46201</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>46202</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58698,7 +58698,7 @@
         <v>44810</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>45698</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>45210</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58917,7 +58917,7 @@
         <v>46204</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>46204</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>46203</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>46204</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>45265</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>46204</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59370,7 +59370,7 @@
         <v>44586</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>46204</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59521,7 +59521,7 @@
         <v>46204</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59594,7 +59594,7 @@
         <v>46204</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59667,7 +59667,7 @@
         <v>45250</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59740,7 +59740,7 @@
         <v>46204</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>46160</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>46205</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>46205</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60037,7 +60037,7 @@
         <v>45112</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>46177</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60183,7 +60183,7 @@
         <v>45274</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45758</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60334,7 +60334,7 @@
         <v>46258</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60412,7 +60412,7 @@
         <v>45476</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60490,7 +60490,7 @@
         <v>46030</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60563,7 +60563,7 @@
         <v>46259</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60641,7 +60641,7 @@
         <v>46260</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60714,7 +60714,7 @@
         <v>46261</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60792,7 +60792,7 @@
         <v>46261</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>46261</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60948,7 +60948,7 @@
         <v>46261</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>46261</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>46261</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>46261</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61255,7 +61255,7 @@
         <v>46261</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61328,7 +61328,7 @@
         <v>46261</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>46261</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61474,7 +61474,7 @@
         <v>46261</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>46261</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>46261</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>46261</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61786,7 +61786,7 @@
         <v>46261</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>46262</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61942,7 +61942,7 @@
         <v>45191</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         <v>46262</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62088,7 +62088,7 @@
         <v>45376</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62161,7 +62161,7 @@
         <v>46262</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>46262</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62317,7 +62317,7 @@
         <v>46219</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>46262</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62468,7 +62468,7 @@
         <v>45075</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62546,7 +62546,7 @@
         <v>46262</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62624,7 +62624,7 @@
         <v>46262</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62702,7 +62702,7 @@
         <v>46266</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>46266</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62858,7 +62858,7 @@
         <v>45562</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62931,7 +62931,7 @@
         <v>45069</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63004,7 +63004,7 @@
         <v>45075</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63077,7 +63077,7 @@
         <v>44805</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63150,7 +63150,7 @@
         <v>46000</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>46230</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45099</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>46230</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63452,7 +63452,7 @@
         <v>44908</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63525,7 +63525,7 @@
         <v>46273</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63598,7 +63598,7 @@
         <v>45639</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>46227</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>45320</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63822,7 +63822,7 @@
         <v>46275</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63895,7 +63895,7 @@
         <v>46163</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63973,7 +63973,7 @@
         <v>46280</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64051,7 +64051,7 @@
         <v>46063</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>45374</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64197,7 +64197,7 @@
         <v>44854</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64270,7 +64270,7 @@
         <v>45205</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64343,7 +64343,7 @@
         <v>45721</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64421,7 +64421,7 @@
         <v>45188</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64499,7 +64499,7 @@
         <v>45483</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64572,7 +64572,7 @@
         <v>45867</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64645,7 +64645,7 @@
         <v>45226</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64718,7 +64718,7 @@
         <v>44818</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64791,7 +64791,7 @@
         <v>44988</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64864,7 +64864,7 @@
         <v>46287</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64937,7 +64937,7 @@
         <v>44875</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>46244</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65083,7 +65083,7 @@
         <v>46204</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65161,7 +65161,7 @@
         <v>46287</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65239,7 +65239,7 @@
         <v>46063</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65312,7 +65312,7 @@
         <v>46287</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65385,7 +65385,7 @@
         <v>45112</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65458,7 +65458,7 @@
         <v>46244</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65536,7 +65536,7 @@
         <v>44796</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65614,7 +65614,7 @@
         <v>46288</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>46288</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65760,7 +65760,7 @@
         <v>45545</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65838,7 +65838,7 @@
         <v>45070</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65911,7 +65911,7 @@
         <v>46246</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>44956</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66062,7 +66062,7 @@
         <v>45300</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         <v>45282</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66208,7 +66208,7 @@
         <v>45602</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>44901</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66354,7 +66354,7 @@
         <v>46247</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66432,7 +66432,7 @@
         <v>45252</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66510,7 +66510,7 @@
         <v>46105</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66583,7 +66583,7 @@
         <v>45082</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66656,7 +66656,7 @@
         <v>45673</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>46252</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>45668</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66875,7 +66875,7 @@
         <v>44914</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>46196</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>46190</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>46035</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67177,7 +67177,7 @@
         <v>45257</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67255,7 +67255,7 @@
         <v>46251</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67333,7 +67333,7 @@
         <v>45688</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67406,7 +67406,7 @@
         <v>46162</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67484,7 +67484,7 @@
         <v>45094</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67562,7 +67562,7 @@
         <v>46244</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67640,7 +67640,7 @@
         <v>46253</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67713,7 +67713,7 @@
         <v>44847</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67786,7 +67786,7 @@
         <v>46049</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>45049</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67932,7 +67932,7 @@
         <v>45264</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>46000</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68078,7 +68078,7 @@
         <v>46255</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68156,7 +68156,7 @@
         <v>46255</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68229,7 +68229,7 @@
         <v>45197</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68302,7 +68302,7 @@
         <v>45984</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68380,7 +68380,7 @@
         <v>46058</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>46058</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>46178</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68604,7 +68604,7 @@
         <v>46254</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68677,7 +68677,7 @@
         <v>46058</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68750,7 +68750,7 @@
         <v>46251</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68828,7 +68828,7 @@
         <v>46065</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68901,7 +68901,7 @@
         <v>46178</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68979,7 +68979,7 @@
         <v>46255</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69052,7 +69052,7 @@
         <v>46244</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69130,7 +69130,7 @@
         <v>46251</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69208,7 +69208,7 @@
         <v>45984</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69286,7 +69286,7 @@
         <v>46262</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69359,7 +69359,7 @@
         <v>46204</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69437,7 +69437,7 @@
         <v>45217</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69510,7 +69510,7 @@
         <v>44564</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69583,7 +69583,7 @@
         <v>44551</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69661,7 +69661,7 @@
         <v>45561</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69734,7 +69734,7 @@
         <v>45063</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69812,7 +69812,7 @@
         <v>45748</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69885,7 +69885,7 @@
         <v>45636</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69958,7 +69958,7 @@
         <v>45085</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70031,7 +70031,7 @@
         <v>45701</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70104,7 +70104,7 @@
         <v>45700</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70177,7 +70177,7 @@
         <v>44855</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70255,7 +70255,7 @@
         <v>44756</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70328,7 +70328,7 @@
         <v>45022</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70401,7 +70401,7 @@
         <v>45463</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70474,7 +70474,7 @@
         <v>45541</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70552,7 +70552,7 @@
         <v>45541</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70630,7 +70630,7 @@
         <v>44587</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70708,7 +70708,7 @@
         <v>45327</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70781,7 +70781,7 @@
         <v>45769</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70854,7 +70854,7 @@
         <v>45590</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70927,7 +70927,7 @@
         <v>45672</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71000,7 +71000,7 @@
         <v>45211</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71073,7 +71073,7 @@
         <v>44566</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71146,7 +71146,7 @@
         <v>45153</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71219,7 +71219,7 @@
         <v>45022</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71297,7 +71297,7 @@
         <v>45779</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71370,7 +71370,7 @@
         <v>45540</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71443,7 +71443,7 @@
         <v>45205</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71516,7 +71516,7 @@
         <v>45622</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71589,7 +71589,7 @@
         <v>45679</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71662,7 +71662,7 @@
         <v>45555</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71735,7 +71735,7 @@
         <v>45174</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71808,7 +71808,7 @@
         <v>44531</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71881,7 +71881,7 @@
         <v>45240</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71954,7 +71954,7 @@
         <v>45178</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72032,7 +72032,7 @@
         <v>44102</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72110,7 +72110,7 @@
         <v>45316</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72188,7 +72188,7 @@
         <v>45315</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72266,7 +72266,7 @@
         <v>44484</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72344,7 +72344,7 @@
         <v>45142</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72422,7 +72422,7 @@
         <v>44550</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72500,7 +72500,7 @@
         <v>45706</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72578,7 +72578,7 @@
         <v>45720</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72656,7 +72656,7 @@
         <v>45707</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72734,7 +72734,7 @@
         <v>45707</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72812,7 +72812,7 @@
         <v>46059</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72890,7 +72890,7 @@
         <v>46059</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72968,7 +72968,7 @@
         <v>46089</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73046,7 +73046,7 @@
         <v>46089</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45404</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>45541</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>46101</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46181</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>46182</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44103</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>46125</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>44505</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44965</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>46055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>46086</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>46091</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46201</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>46216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>46053</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45566</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45187</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45440</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>46031</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>46185</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>46188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>46201</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>46289</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>46251</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>46253</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>46107</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>46261</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>46062</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45699</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>44505</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>44515</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>44829</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44958</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>45089</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45883</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>44955</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44949</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45446</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45252</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45930</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45800</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>45800</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45194</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>44663</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>45868</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45981</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45730</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>46105</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>46104</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>46114</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>46119</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>46133</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>46021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>46030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>46045</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>46057</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45899</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>46059</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>46148</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>46069</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>46084</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>46093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>46097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>46168</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>46169</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>46175</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>46182</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45453</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>46219</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46269</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>46281</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>46239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>46239</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>46239</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>46254</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45177</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>46301</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>46261</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>46262</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46303</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>46262</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45064</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45699</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45706</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46122</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>44868</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44505</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44865</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44774</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44510</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44501</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44760</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44873</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44512</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44854</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44635</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44596</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44595</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44861</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44635</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44523</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44501</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44603</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44519</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44714</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44854</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44595</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>44817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44847</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44672</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45365</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45252</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>45480</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45415</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45576</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45087</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45649</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45327</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44901</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45212</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45288</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45561</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>45460</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45049</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>44501</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45721</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45541</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44797</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45121</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44918</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>45327</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45672</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45512</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45701</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>45467</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45265</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>45226</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45414</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44551</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45252</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45279</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45884</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44510</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45281</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45636</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45159</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45567</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45069</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45883</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45883</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45197</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45883</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44854</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45884</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45884</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45884</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45887</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45800</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45545</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45552</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45888</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45330</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45540</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45887</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45483</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45300</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>44756</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45191</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>44918</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45769</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45891</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45896</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45898</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45667</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45899</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45722</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45540</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>44845</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44564</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45476</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45022</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45483</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45544</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45070</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45343</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45649</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45085</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45112</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44972</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45615</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45721</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45910</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45910</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45666</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45779</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>44875</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45540</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45916</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45174</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45748</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45240</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44587</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45555</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45622</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>44855</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45205</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45178</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44531</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45679</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45162</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45520</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45919</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45112</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45919</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>44586</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45120</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45525</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45925</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45099</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45926</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45926</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45925</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45191</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>45639</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45930</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44549</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45475</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44813</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45188</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45404</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45541</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45701</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45418</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45252</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45278</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44566</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45075</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45153</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45153</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45614</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45673</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45933</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45763</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45800</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45800</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45800</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45799</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45112</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45638</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45800</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>45590</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>45933</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45933</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45799</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45799</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45936</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45769</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45390</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45126</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45937</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45937</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45673</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45805</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44956</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45217</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45082</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44810</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45938</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45212</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45938</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45810</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45094</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>45182</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>45938</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>45939</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45205</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45943</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45208</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45930</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45930</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45945</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45946</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45211</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>44988</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45666</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45945</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45698</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45209</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45240</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45261</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45261</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45245</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45478</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45819</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45819</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44797</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45645</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45825</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45701</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45701</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45615</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45827</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45022</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45688</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45671</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45832</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45831</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45769</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45957</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45833</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45250</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45251</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45589</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45463</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45226</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45602</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45840</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45968</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>44804</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45842</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45408</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45615</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45971</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45845</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45971</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45971</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45762</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>44582</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45693</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44744</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45978</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45730</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45246</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45649</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45649</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45321</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45530</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45866</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45863</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45866</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45975</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45867</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45226</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45870</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45977</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45979</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45196</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45188</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>44796</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44784</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45873</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>45873</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44846</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45873</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45873</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45153</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>45488</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45670</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44843</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45706</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>44586</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45191</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45264</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45771</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>46095</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45265</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>45211</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>46098</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45981</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>46099</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>46099</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46099</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>46099</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46098</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46100</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>46100</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45985</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45293</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>46101</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45983</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45700</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46101</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45660</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>46105</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>45984</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>46107</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45257</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45984</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45984</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>46107</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>46106</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45540</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>46107</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>45523</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>46111</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>46108</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>46111</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46111</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>46108</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45992</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45992</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45755</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45992</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46112</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45210</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>44908</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45260</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>44544</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45636</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>46115</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>46115</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>46115</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>45721</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45721</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>46115</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>46114</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>46115</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46119</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>46119</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>46116</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>46116</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>46119</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>46115</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>46116</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>46119</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>46119</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46119</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>46120</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>46121</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>44988</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>44988</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>46121</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46126</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45999</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>46126</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>46126</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>46099</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>46000</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45022</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>46130</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46132</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>46132</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45986</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>46129</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>46128</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>46132</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45374</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45376</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46128</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45999</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>46128</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>46091</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>45562</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>46132</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45271</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>46091</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>46129</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>46129</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>46129</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>46129</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>46000</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>46129</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46133</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45070</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45075</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46136</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>46091</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>46135</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>46042</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>46136</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44805</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>46135</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46086</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>46093</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46065</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>44656</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>46090</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45558</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45709</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>46048</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>46013</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45356</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45404</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>44481</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45075</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45240</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>46021</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45303</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>46065</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>44818</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>46057</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45476</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>46063</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45905</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>46055</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>46031</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45735</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45779</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>46031</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>46034</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46035</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>46063</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>46069</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>46036</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>46065</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>46036</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>46036</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45103</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>46036</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>46063</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>46071</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45730</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>45730</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>46036</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>46035</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45320</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>46035</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>46052</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>46038</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>46037</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>46042</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45238</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45562</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45668</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>46030</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45537</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45268</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>46104</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45063</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>46038</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>46044</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>46043</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>45595</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>46044</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46061</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>46043</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45917</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>46046</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45728</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>46140</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>46058</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>46045</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>46085</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>46080</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>46036</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45602</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>46069</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45883</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>46048</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>46037</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>46029</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46045</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45327</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>46134</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>46105</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>46030</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>46071</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>46050</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>44949</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>46043</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>46058</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>46051</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>46090</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>46090</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>46051</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>46050</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50832,7 +50832,7 @@
         <v>46055</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>46055</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>46043</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>46055</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51134,7 +51134,7 @@
         <v>46056</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>46141</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>46056</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>46056</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>46062</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>46058</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>46072</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>46058</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>46031</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>46058</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>46062</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>46038</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>46063</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         <v>46063</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>46063</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52239,7 +52239,7 @@
         <v>46063</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>46063</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>46064</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>46065</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>46063</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>46065</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52677,7 +52677,7 @@
         <v>46142</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         <v>46066</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>46066</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52896,7 +52896,7 @@
         <v>46066</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52969,7 +52969,7 @@
         <v>46065</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>46148</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>46065</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>46147</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>46147</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>46147</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>46069</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>46147</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53573,7 +53573,7 @@
         <v>46147</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46150</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>46069</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>46072</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>46071</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>46072</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>46072</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>46076</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46031</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>46043</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46086</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>46074</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>46048</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46151</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>46086</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>46076</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>46050</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54849,7 +54849,7 @@
         <v>46073</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54927,7 +54927,7 @@
         <v>46073</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>46079</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>46153</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>46034</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>46036</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55297,7 +55297,7 @@
         <v>46078</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55370,7 +55370,7 @@
         <v>46080</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>46035</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55516,7 +55516,7 @@
         <v>46080</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>46085</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>46084</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>46084</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>46085</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>46085</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>46037</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56037,7 +56037,7 @@
         <v>46108</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56115,7 +56115,7 @@
         <v>46084</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>46084</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>46094</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>46086</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56417,7 +56417,7 @@
         <v>46087</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>46086</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>46086</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>46086</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56729,7 +56729,7 @@
         <v>46087</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56807,7 +56807,7 @@
         <v>46086</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>46086</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56963,7 +56963,7 @@
         <v>46087</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>46086</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57109,7 +57109,7 @@
         <v>46086</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>46086</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>46086</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>46108</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>46090</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>46104</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>46043</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>46090</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>46091</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57786,7 +57786,7 @@
         <v>46091</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57864,7 +57864,7 @@
         <v>46092</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>46093</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>46092</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>46092</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>46093</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>46092</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46036</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>46094</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>46095</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>46095</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58614,7 +58614,7 @@
         <v>46095</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58687,7 +58687,7 @@
         <v>46097</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>46097</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>46094</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>46095</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>46097</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>46161</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>46034</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>46107</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>46163</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>46163</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46030</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>46163</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59593,7 +59593,7 @@
         <v>46163</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46163</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>46163</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59827,7 +59827,7 @@
         <v>46165</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>46165</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>46165</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>46167</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>46168</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>46165</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>46165</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>46168</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>46169</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>46169</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>46169</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>46169</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>46169</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>46052</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>46171</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>46171</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>46175</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>46175</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>46045</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>46175</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>46045</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>46177</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>46069</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>46177</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>46176</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>46176</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>46178</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>46178</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>46178</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         <v>46183</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62092,7 +62092,7 @@
         <v>46185</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62165,7 +62165,7 @@
         <v>46185</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62238,7 +62238,7 @@
         <v>46185</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62311,7 +62311,7 @@
         <v>46185</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62384,7 +62384,7 @@
         <v>46184</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>46184</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>46101</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62608,7 +62608,7 @@
         <v>46191</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62681,7 +62681,7 @@
         <v>46034</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>46190</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62827,7 +62827,7 @@
         <v>46195</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62905,7 +62905,7 @@
         <v>46196</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>46196</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>46196</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63134,7 +63134,7 @@
         <v>46196</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63212,7 +63212,7 @@
         <v>46201</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63290,7 +63290,7 @@
         <v>46198</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63363,7 +63363,7 @@
         <v>46202</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>46203</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63509,7 +63509,7 @@
         <v>46204</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63587,7 +63587,7 @@
         <v>46204</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>46204</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>46205</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63811,7 +63811,7 @@
         <v>46204</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>46204</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>46205</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>46160</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>46177</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64186,7 +64186,7 @@
         <v>46030</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64259,7 +64259,7 @@
         <v>46219</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64332,7 +64332,7 @@
         <v>46266</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>46266</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64488,7 +64488,7 @@
         <v>46000</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64561,7 +64561,7 @@
         <v>46227</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64639,7 +64639,7 @@
         <v>46273</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64712,7 +64712,7 @@
         <v>46230</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>46230</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64868,7 +64868,7 @@
         <v>46275</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
         <v>46063</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65014,7 +65014,7 @@
         <v>46280</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>46204</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65170,7 +65170,7 @@
         <v>46287</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>46288</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65316,7 +65316,7 @@
         <v>46288</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>46287</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>46244</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>46244</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65613,7 +65613,7 @@
         <v>46287</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>46247</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46246</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65847,7 +65847,7 @@
         <v>46190</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>46162</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>46035</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>46196</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66154,7 +66154,7 @@
         <v>46251</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>46253</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66305,7 +66305,7 @@
         <v>46252</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>46058</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66451,7 +66451,7 @@
         <v>46126</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66524,7 +66524,7 @@
         <v>46091</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66602,7 +66602,7 @@
         <v>46095</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66675,7 +66675,7 @@
         <v>46115</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66748,7 +66748,7 @@
         <v>46178</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66826,7 +66826,7 @@
         <v>46058</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66899,7 +66899,7 @@
         <v>46058</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66972,7 +66972,7 @@
         <v>46251</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67050,7 +67050,7 @@
         <v>46178</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67128,7 +67128,7 @@
         <v>46128</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67201,7 +67201,7 @@
         <v>46132</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67279,7 +67279,7 @@
         <v>46095</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67352,7 +67352,7 @@
         <v>46000</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67425,7 +67425,7 @@
         <v>46244</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67503,7 +67503,7 @@
         <v>46255</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67576,7 +67576,7 @@
         <v>46065</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67649,7 +67649,7 @@
         <v>46300</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67722,7 +67722,7 @@
         <v>46204</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67800,7 +67800,7 @@
         <v>45984</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67878,7 +67878,7 @@
         <v>45926</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67956,7 +67956,7 @@
         <v>46178</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68034,7 +68034,7 @@
         <v>46254</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68107,7 +68107,7 @@
         <v>46255</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>46255</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68258,7 +68258,7 @@
         <v>45984</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68336,7 +68336,7 @@
         <v>46049</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68409,7 +68409,7 @@
         <v>46251</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68487,7 +68487,7 @@
         <v>46244</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68565,7 +68565,7 @@
         <v>46105</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68638,7 +68638,7 @@
         <v>46044</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68711,7 +68711,7 @@
         <v>46258</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68789,7 +68789,7 @@
         <v>46301</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68862,7 +68862,7 @@
         <v>46092</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68935,7 +68935,7 @@
         <v>46204</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69008,7 +69008,7 @@
         <v>46204</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69081,7 +69081,7 @@
         <v>46259</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69159,7 +69159,7 @@
         <v>46262</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69237,7 +69237,7 @@
         <v>46261</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69315,7 +69315,7 @@
         <v>46261</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69393,7 +69393,7 @@
         <v>46085</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69471,7 +69471,7 @@
         <v>46261</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69549,7 +69549,7 @@
         <v>46304</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69627,7 +69627,7 @@
         <v>46261</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69705,7 +69705,7 @@
         <v>46261</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69783,7 +69783,7 @@
         <v>46262</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69856,7 +69856,7 @@
         <v>46262</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69934,7 +69934,7 @@
         <v>46163</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70012,7 +70012,7 @@
         <v>46163</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70085,7 +70085,7 @@
         <v>46261</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70163,7 +70163,7 @@
         <v>46261</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70236,7 +70236,7 @@
         <v>46261</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70309,7 +70309,7 @@
         <v>46261</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70387,7 +70387,7 @@
         <v>46261</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70460,7 +70460,7 @@
         <v>46260</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70533,7 +70533,7 @@
         <v>46262</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70611,7 +70611,7 @@
         <v>46261</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70689,7 +70689,7 @@
         <v>46261</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70767,7 +70767,7 @@
         <v>46262</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70840,7 +70840,7 @@
         <v>46262</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70918,7 +70918,7 @@
         <v>46261</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70991,7 +70991,7 @@
         <v>46262</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71069,7 +71069,7 @@
         <v>46262</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71147,7 +71147,7 @@
         <v>46062</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71220,7 +71220,7 @@
         <v>46261</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71298,7 +71298,7 @@
         <v>46261</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71376,7 +71376,7 @@
         <v>46178</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71454,7 +71454,7 @@
         <v>45867</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71527,7 +71527,7 @@
         <v>44102</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71605,7 +71605,7 @@
         <v>44550</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71683,7 +71683,7 @@
         <v>45316</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71761,7 +71761,7 @@
         <v>45315</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71839,7 +71839,7 @@
         <v>45706</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71917,7 +71917,7 @@
         <v>44484</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71995,7 +71995,7 @@
         <v>45142</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72073,7 +72073,7 @@
         <v>45720</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72151,7 +72151,7 @@
         <v>45707</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>45707</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72307,7 +72307,7 @@
         <v>46059</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72385,7 +72385,7 @@
         <v>46059</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72463,7 +72463,7 @@
         <v>46089</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72541,7 +72541,7 @@
         <v>46089</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45404</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>45541</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>46101</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46181</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>46182</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44103</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>46125</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>44505</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44965</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>46055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>46086</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>46091</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46201</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>46216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>46053</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45566</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45187</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45440</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>46031</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>46185</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>46188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>46201</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>46289</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>46251</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>46253</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>46107</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>46261</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>46062</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45699</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>44505</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>44515</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>44829</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44958</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>45089</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45883</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>44955</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44949</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45446</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45252</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45930</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45800</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>45800</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45194</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>44663</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>45868</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45981</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45730</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>46105</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>46104</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>46114</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>46119</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>46133</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>46021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>46030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>46045</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>46057</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45899</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>46059</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>46148</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>46069</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>46084</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>46093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>46097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>46168</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>46169</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>46175</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>46182</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45453</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>46219</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46269</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>46281</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>46239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>46239</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>46239</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>46254</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45177</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>46301</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>46261</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>46262</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46303</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>46262</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45064</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45699</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45706</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46122</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>44868</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44505</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44865</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44774</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44510</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44501</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44760</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44873</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44512</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44854</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44635</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44596</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44595</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44861</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44635</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44523</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44501</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44603</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44519</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44714</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44854</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44595</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>44817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44847</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44672</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45365</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45252</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>45480</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45415</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45576</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45087</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45649</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45327</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44901</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45212</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45288</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45561</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>45460</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45049</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>44501</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45721</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45541</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44797</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45121</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44918</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>45327</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45672</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45512</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45701</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>45467</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45265</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>45226</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45414</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44551</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45252</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45279</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45884</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44510</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45281</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45636</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45159</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45567</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45069</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45883</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45883</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45197</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45883</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44854</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45884</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45884</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45884</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45887</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45800</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45545</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45552</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45888</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45330</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45540</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45887</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45483</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45300</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>44756</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45191</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>44918</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45769</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45891</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45896</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45898</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45667</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45899</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45722</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45540</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>44845</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44564</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45476</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45022</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45483</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45544</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45070</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45343</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45649</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45085</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45112</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44972</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45615</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45721</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45910</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45910</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45666</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45779</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>44875</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45540</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45916</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45174</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45748</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45240</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44587</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45555</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45622</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>44855</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45205</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45178</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44531</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45679</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45162</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45520</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45919</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45112</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45919</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>44586</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45120</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45525</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45925</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45099</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45926</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45926</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45925</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45191</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>45639</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45930</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44549</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45475</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44813</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45188</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45404</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45541</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45701</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45418</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45252</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45278</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44566</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45075</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45153</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45153</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45614</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45673</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45933</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45763</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45800</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45800</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45800</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45799</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45112</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45638</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45800</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>45590</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>45933</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45933</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45799</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45799</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45936</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45769</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45390</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45126</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45937</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45937</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45673</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45805</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44956</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45217</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45082</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44810</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45938</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45212</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45938</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45810</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45094</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>45182</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>45938</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>45939</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45205</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45943</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45208</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45930</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45930</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45945</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45946</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45211</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>44988</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45666</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45945</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45698</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45209</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45240</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45261</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45261</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45245</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45478</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45819</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45819</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44797</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45645</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45825</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45701</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45701</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45615</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45827</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45022</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45688</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45671</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45832</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45831</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45769</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45957</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45833</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45250</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45251</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45589</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45463</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45226</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45602</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45840</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45968</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>44804</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45842</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45408</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45615</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45971</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45845</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45971</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45971</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45762</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>44582</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45693</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44744</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45978</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45730</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45246</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45649</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45649</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45321</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45530</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45866</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45863</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45866</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45975</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45867</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45226</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45870</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45977</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45979</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45196</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45188</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>44796</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44784</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45873</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>45873</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44846</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45873</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45873</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45153</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>45488</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45670</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44843</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45706</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>44586</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45191</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45264</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45771</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>46095</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45265</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>45211</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>46098</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45981</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>46099</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>46099</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46099</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>46099</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46098</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46100</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>46100</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45985</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45293</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>46101</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45983</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45700</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46101</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45660</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>46105</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>45984</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>46107</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45257</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45984</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45984</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>46107</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>46106</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45540</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>46107</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>45523</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>46111</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>46108</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>46111</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46111</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>46108</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45992</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45992</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45755</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45992</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46112</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45210</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>44908</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45260</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>44544</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45636</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>46115</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>46115</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>46115</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>45721</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45721</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>46115</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>46114</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>46115</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46119</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>46119</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>46116</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>46116</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>46119</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>46115</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>46116</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>46119</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>46119</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46119</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>46120</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>46121</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>44988</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>44988</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>46121</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46126</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45999</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>46126</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>46126</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>46099</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>46000</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45022</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>46130</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46132</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>46132</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45986</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>46129</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>46128</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>46132</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45374</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45376</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46128</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45999</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>46128</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>46091</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>45562</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>46132</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45271</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>46091</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>46129</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>46129</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>46129</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>46129</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>46000</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>46129</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46133</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45070</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45075</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46136</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>46091</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>46135</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>46042</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>46136</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44805</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>46135</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46086</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>46093</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46065</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>44656</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>46090</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45558</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45709</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>46048</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>46013</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45356</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45404</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>44481</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45075</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45240</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>46021</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45303</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>46065</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>44818</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>46057</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45476</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>46063</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45905</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>46055</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>46031</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45735</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45779</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>46031</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>46034</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46035</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>46063</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>46069</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>46036</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>46065</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>46036</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>46036</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45103</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>46036</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>46063</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>46071</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45730</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>45730</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>46036</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>46035</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45320</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>46035</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>46052</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>46038</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>46037</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>46042</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45238</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45562</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45668</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>46030</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45537</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45268</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>46104</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45063</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>46038</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>46044</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>46043</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>45595</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>46044</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46061</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>46043</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45917</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>46046</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45728</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>46140</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>46058</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>46045</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>46085</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>46080</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>46036</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45602</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>46069</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45883</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>46048</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>46037</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>46029</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46045</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45327</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>46134</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>46105</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>46030</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>46071</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>46050</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>44949</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>46043</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>46058</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>46051</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>46090</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>46090</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>46051</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>46050</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50832,7 +50832,7 @@
         <v>46055</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>46055</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>46043</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>46055</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51134,7 +51134,7 @@
         <v>46056</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>46141</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>46056</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>46056</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>46062</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>46058</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>46072</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>46058</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>46031</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>46058</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>46062</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>46038</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>46063</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         <v>46063</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>46063</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52239,7 +52239,7 @@
         <v>46063</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>46063</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>46064</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>46065</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>46063</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>46065</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52677,7 +52677,7 @@
         <v>46142</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         <v>46066</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>46066</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52896,7 +52896,7 @@
         <v>46066</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52969,7 +52969,7 @@
         <v>46065</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>46148</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>46065</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>46147</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>46147</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>46147</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>46069</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>46147</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53573,7 +53573,7 @@
         <v>46147</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46150</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>46069</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>46072</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>46071</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>46072</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>46072</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>46076</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46031</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>46043</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46086</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>46074</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>46048</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46151</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>46086</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>46076</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>46050</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54849,7 +54849,7 @@
         <v>46073</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54927,7 +54927,7 @@
         <v>46073</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>46079</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>46153</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>46034</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>46036</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55297,7 +55297,7 @@
         <v>46078</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55370,7 +55370,7 @@
         <v>46080</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>46035</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55516,7 +55516,7 @@
         <v>46080</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>46085</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>46084</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>46084</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>46085</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>46085</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>46037</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56037,7 +56037,7 @@
         <v>46108</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56115,7 +56115,7 @@
         <v>46084</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>46084</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>46094</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>46086</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56417,7 +56417,7 @@
         <v>46087</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>46086</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>46086</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>46086</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56729,7 +56729,7 @@
         <v>46087</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56807,7 +56807,7 @@
         <v>46086</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>46086</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56963,7 +56963,7 @@
         <v>46087</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>46086</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57109,7 +57109,7 @@
         <v>46086</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>46086</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>46086</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>46108</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>46090</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>46104</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>46043</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>46090</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>46091</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57786,7 +57786,7 @@
         <v>46091</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57864,7 +57864,7 @@
         <v>46092</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>46093</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>46092</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>46092</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>46093</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>46092</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46036</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>46094</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>46095</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>46095</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58614,7 +58614,7 @@
         <v>46095</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58687,7 +58687,7 @@
         <v>46097</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>46097</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>46094</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>46095</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>46097</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>46161</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>46034</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>46107</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>46163</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>46163</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46030</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>46163</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59593,7 +59593,7 @@
         <v>46163</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46163</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>46163</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59827,7 +59827,7 @@
         <v>46165</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>46165</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>46165</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>46167</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>46168</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>46165</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>46165</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>46168</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>46169</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>46169</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>46169</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>46169</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>46169</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>46052</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>46171</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>46171</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>46175</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>46175</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>46045</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>46175</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>46045</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>46177</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>46069</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>46177</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>46176</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>46176</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>46178</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>46178</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>46178</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         <v>46183</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62092,7 +62092,7 @@
         <v>46185</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62165,7 +62165,7 @@
         <v>46185</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62238,7 +62238,7 @@
         <v>46185</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62311,7 +62311,7 @@
         <v>46185</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62384,7 +62384,7 @@
         <v>46184</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>46184</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>46101</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62608,7 +62608,7 @@
         <v>46191</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62681,7 +62681,7 @@
         <v>46034</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>46190</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62827,7 +62827,7 @@
         <v>46195</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62905,7 +62905,7 @@
         <v>46196</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>46196</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>46196</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63134,7 +63134,7 @@
         <v>46196</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63212,7 +63212,7 @@
         <v>46201</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63290,7 +63290,7 @@
         <v>46198</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63363,7 +63363,7 @@
         <v>46202</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>46203</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63509,7 +63509,7 @@
         <v>46204</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63587,7 +63587,7 @@
         <v>46204</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>46204</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>46205</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63811,7 +63811,7 @@
         <v>46204</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>46204</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>46205</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>46160</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>46177</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64186,7 +64186,7 @@
         <v>46030</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64259,7 +64259,7 @@
         <v>46219</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64332,7 +64332,7 @@
         <v>46266</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>46266</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64488,7 +64488,7 @@
         <v>46000</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64561,7 +64561,7 @@
         <v>46227</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64639,7 +64639,7 @@
         <v>46273</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64712,7 +64712,7 @@
         <v>46230</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>46230</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64868,7 +64868,7 @@
         <v>46275</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
         <v>46063</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65014,7 +65014,7 @@
         <v>46280</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>46204</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65170,7 +65170,7 @@
         <v>46287</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>46288</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65316,7 +65316,7 @@
         <v>46288</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>46287</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>46244</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>46244</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65613,7 +65613,7 @@
         <v>46287</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>46247</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46246</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65847,7 +65847,7 @@
         <v>46190</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>46162</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>46035</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>46196</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66154,7 +66154,7 @@
         <v>46251</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>46253</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66305,7 +66305,7 @@
         <v>46252</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>46058</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66451,7 +66451,7 @@
         <v>46126</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66524,7 +66524,7 @@
         <v>46091</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66602,7 +66602,7 @@
         <v>46095</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66675,7 +66675,7 @@
         <v>46115</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66748,7 +66748,7 @@
         <v>46178</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66826,7 +66826,7 @@
         <v>46058</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66899,7 +66899,7 @@
         <v>46058</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66972,7 +66972,7 @@
         <v>46251</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67050,7 +67050,7 @@
         <v>46178</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67128,7 +67128,7 @@
         <v>46128</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67201,7 +67201,7 @@
         <v>46132</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67279,7 +67279,7 @@
         <v>46095</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67352,7 +67352,7 @@
         <v>46000</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67425,7 +67425,7 @@
         <v>46244</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67503,7 +67503,7 @@
         <v>46255</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67576,7 +67576,7 @@
         <v>46065</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67649,7 +67649,7 @@
         <v>46300</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67722,7 +67722,7 @@
         <v>46204</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67800,7 +67800,7 @@
         <v>45984</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67878,7 +67878,7 @@
         <v>45926</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67956,7 +67956,7 @@
         <v>46178</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68034,7 +68034,7 @@
         <v>46254</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68107,7 +68107,7 @@
         <v>46255</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>46255</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68258,7 +68258,7 @@
         <v>45984</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68336,7 +68336,7 @@
         <v>46049</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68409,7 +68409,7 @@
         <v>46251</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68487,7 +68487,7 @@
         <v>46244</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68565,7 +68565,7 @@
         <v>46105</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68638,7 +68638,7 @@
         <v>46044</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68711,7 +68711,7 @@
         <v>46258</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68789,7 +68789,7 @@
         <v>46301</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68862,7 +68862,7 @@
         <v>46092</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68935,7 +68935,7 @@
         <v>46204</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69008,7 +69008,7 @@
         <v>46204</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69081,7 +69081,7 @@
         <v>46259</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69159,7 +69159,7 @@
         <v>46262</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69237,7 +69237,7 @@
         <v>46261</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69315,7 +69315,7 @@
         <v>46261</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69393,7 +69393,7 @@
         <v>46085</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69471,7 +69471,7 @@
         <v>46261</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69549,7 +69549,7 @@
         <v>46304</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69627,7 +69627,7 @@
         <v>46261</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69705,7 +69705,7 @@
         <v>46261</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69783,7 +69783,7 @@
         <v>46262</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69856,7 +69856,7 @@
         <v>46262</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69934,7 +69934,7 @@
         <v>46163</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70012,7 +70012,7 @@
         <v>46163</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70085,7 +70085,7 @@
         <v>46261</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70163,7 +70163,7 @@
         <v>46261</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70236,7 +70236,7 @@
         <v>46261</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70309,7 +70309,7 @@
         <v>46261</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70387,7 +70387,7 @@
         <v>46261</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70460,7 +70460,7 @@
         <v>46260</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70533,7 +70533,7 @@
         <v>46262</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70611,7 +70611,7 @@
         <v>46261</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70689,7 +70689,7 @@
         <v>46261</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70767,7 +70767,7 @@
         <v>46262</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70840,7 +70840,7 @@
         <v>46262</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70918,7 +70918,7 @@
         <v>46261</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70991,7 +70991,7 @@
         <v>46262</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71069,7 +71069,7 @@
         <v>46262</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71147,7 +71147,7 @@
         <v>46062</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71220,7 +71220,7 @@
         <v>46261</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71298,7 +71298,7 @@
         <v>46261</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71376,7 +71376,7 @@
         <v>46178</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71454,7 +71454,7 @@
         <v>45867</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71527,7 +71527,7 @@
         <v>44102</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71605,7 +71605,7 @@
         <v>44550</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71683,7 +71683,7 @@
         <v>45316</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71761,7 +71761,7 @@
         <v>45315</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71839,7 +71839,7 @@
         <v>45706</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71917,7 +71917,7 @@
         <v>44484</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71995,7 +71995,7 @@
         <v>45142</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72073,7 +72073,7 @@
         <v>45720</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72151,7 +72151,7 @@
         <v>45707</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>45707</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72307,7 +72307,7 @@
         <v>46059</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72385,7 +72385,7 @@
         <v>46059</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72463,7 +72463,7 @@
         <v>46089</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72541,7 +72541,7 @@
         <v>46089</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>45957</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45677</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>46086</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45541</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>46101</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>45404</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44103</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>46125</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44505</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>46055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>46091</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>46201</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>46216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>46053</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45440</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>46031</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>46185</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>45566</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>46201</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>45187</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>46289</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>46107</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>46062</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>46261</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>45721</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>45699</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>44588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44505</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44515</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>44829</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45252</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44949</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45730</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44663</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45194</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>46045</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>46057</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>45899</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>46148</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>45930</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45089</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>46168</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>46169</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45446</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>46021</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>46175</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>46030</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>46182</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>46059</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>46069</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>46084</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>46093</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>46097</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46104</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>46105</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>46114</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>46119</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>46133</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45453</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>46219</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>46281</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>46239</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>46239</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>46239</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44955</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>46162</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>46303</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>46301</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46261</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>46262</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>46262</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45800</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45800</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>46269</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45868</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45883</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45319</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45064</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45706</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45699</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45706</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>46122</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>44868</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44774</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44510</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44501</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44505</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44760</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44873</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>44854</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>44512</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44876</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>44635</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44596</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44595</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44519</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44501</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>44595</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>44861</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44854</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>44714</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>44635</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>44603</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>44817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44672</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>45022</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45615</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44656</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44846</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44988</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>45191</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>45523</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45671</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44845</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45281</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>45212</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>45540</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45240</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45540</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45649</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45771</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45693</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>45265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45365</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44994</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45701</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45544</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45191</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45638</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45169</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44988</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>44744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45408</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45162</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>45162</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45730</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45649</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45208</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45649</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45589</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45567</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45615</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45260</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45615</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>44813</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45226</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45480</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45251</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>44797</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>44582</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44804</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45279</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45667</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45252</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45240</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45540</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45884</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45887</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45905</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45709</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>46080</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>46030</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>46134</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>45800</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>45884</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45884</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45238</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>46061</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46037</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>46052</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>46063</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45562</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>46104</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>46136</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>46093</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45356</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45467</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45330</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>46046</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45887</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45558</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45602</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45888</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45884</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44501</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45891</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44549</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45735</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>46071</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45701</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45769</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46136</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46069</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45121</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45769</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45917</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45552</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45390</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>46048</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>45537</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45779</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45899</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>46048</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>46042</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45252</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45706</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45660</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45728</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46057</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45898</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45670</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>46071</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>46069</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>46065</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>46063</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>46058</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>46058</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46090</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>46065</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>46140</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>46055</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>46063</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>46141</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45883</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>46085</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>46043</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>46031</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>46090</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45246</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45478</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>46030</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>45120</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>46038</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>45910</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45910</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>46105</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>46142</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>46072</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>46065</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>46147</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45916</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>46147</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>46147</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44586</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>45919</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45919</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>46147</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>46147</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>46038</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45211</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45925</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45925</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>46148</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45070</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45926</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45636</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>45087</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45530</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>46151</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>45930</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>46050</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45931</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46035</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45933</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45933</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>46150</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45933</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45512</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>46043</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45936</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45460</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45937</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45153</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45938</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45939</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45938</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45937</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45943</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45261</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44918</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>46153</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45945</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45576</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45271</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45930</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45930</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>46108</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44918</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45945</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>46079</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45946</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45946</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45245</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45404</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>46048</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>45069</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45666</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45755</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>46086</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46086</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45415</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>44994</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44994</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45957</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45414</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>46094</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45649</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46104</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45343</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>46108</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>46161</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>46107</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>45730</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45730</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>46034</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45971</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45971</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45968</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45261</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>46163</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45971</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45293</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>45293</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46163</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45975</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>46163</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>46030</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45327</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45977</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46163</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45978</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45979</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>46163</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>46163</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>46165</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>45983</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>45984</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45984</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45984</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45321</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45268</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>46167</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45981</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45981</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45985</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>46165</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>46165</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>46165</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>46165</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45986</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45153</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45992</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45992</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45992</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45992</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>46169</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45196</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>46168</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>46168</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>46169</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46169</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>45999</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45288</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44797</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45645</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>46169</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>46169</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45226</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46000</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>46000</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45701</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45986</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44544</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>45999</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45999</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45162</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>44988</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46171</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45159</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44949</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>46171</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>46045</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>46013</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>46045</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45103</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>46052</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45722</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>46021</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45666</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46031</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>46031</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>44972</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45212</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>46034</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>46035</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45721</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45721</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45721</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46175</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>46035</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46175</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>46176</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>46176</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>46175</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>46035</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>46037</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>46036</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>46036</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>46178</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>46036</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
         <v>46036</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>46178</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46178</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>46036</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>46069</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>46038</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>46043</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>46042</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>46043</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>46177</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>46177</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>46044</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>46044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45075</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>46045</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45483</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46045</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46050</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>46050</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46051</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>46051</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>46055</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46055</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45182</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>46055</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>46056</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>46043</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>46056</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>46056</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>46184</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>44843</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46058</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>46058</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>46058</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45327</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>46063</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>46184</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>46063</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>46062</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>46063</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>46063</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>46063</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>46062</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>46063</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>46183</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46065</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>46065</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>46064</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>46065</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>46069</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>46066</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>46069</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>46185</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>44810</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>46066</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         <v>46066</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>46185</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>46071</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45698</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>46073</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46073</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>46185</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>46072</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>45210</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>46072</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>46072</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>46076</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>46185</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>45265</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>46074</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>46076</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>44586</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>46031</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>46078</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>46034</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>46080</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45250</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44420,7 +44420,7 @@
         <v>46036</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>46080</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>46084</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>46084</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>46084</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>45112</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>46037</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>46084</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45014,7 +45014,7 @@
         <v>46086</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>46085</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>46086</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>46086</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>46085</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>46086</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>46085</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>46086</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>46086</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>46086</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>46086</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>46086</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>46086</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>46087</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>46090</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>46087</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>46087</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>46090</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>46190</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>46101</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>46092</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>46092</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>46091</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46773,7 +46773,7 @@
         <v>46092</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>46043</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>46034</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>46191</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>46092</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>46195</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45274</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>46091</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>46093</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>46094</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>46093</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>46036</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>46094</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>46097</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>46097</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>46095</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>46095</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>46095</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>46095</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>46098</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>46098</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>46095</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>46097</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>46099</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48560,7 +48560,7 @@
         <v>46100</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>45476</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>46100</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48789,7 +48789,7 @@
         <v>46196</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>46196</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>46099</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>46196</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>46099</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>46099</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>46196</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>46101</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>46101</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>46106</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45191</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>46105</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>46107</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49778,7 +49778,7 @@
         <v>46107</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>46107</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>46108</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>46108</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45376</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>46111</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50236,7 +50236,7 @@
         <v>46111</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>46198</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50387,7 +50387,7 @@
         <v>46111</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50465,7 +50465,7 @@
         <v>46112</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45075</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>46114</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>46115</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50762,7 +50762,7 @@
         <v>46116</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>46115</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>46115</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>46116</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>46115</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>46116</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51200,7 +51200,7 @@
         <v>46115</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>46115</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>46119</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>46119</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>46119</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51580,7 +51580,7 @@
         <v>45562</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>46201</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51731,7 +51731,7 @@
         <v>46119</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>46119</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         <v>46119</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51965,7 +51965,7 @@
         <v>46120</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>45069</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>46202</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>46121</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>46121</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>46126</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45075</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52491,7 +52491,7 @@
         <v>44805</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>46126</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52637,7 +52637,7 @@
         <v>46126</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>46129</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52788,7 +52788,7 @@
         <v>46129</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52866,7 +52866,7 @@
         <v>46129</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52939,7 +52939,7 @@
         <v>46128</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>46129</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>46099</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>46129</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53251,7 +53251,7 @@
         <v>46129</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>46128</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45099</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>46128</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>44908</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>46132</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>46204</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>46204</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>46130</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>46132</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45639</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>46091</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>46132</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>46133</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>46132</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54376,7 +54376,7 @@
         <v>46091</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>46203</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>46135</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54605,7 +54605,7 @@
         <v>46204</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54678,7 +54678,7 @@
         <v>46135</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54756,7 +54756,7 @@
         <v>46086</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54834,7 +54834,7 @@
         <v>45320</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>46065</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>46090</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>46204</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         <v>46091</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>46204</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45476</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>46036</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45303</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45374</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>44854</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>45595</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55725,7 +55725,7 @@
         <v>45205</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>46160</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>46205</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>46205</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45721</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45188</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56178,7 +56178,7 @@
         <v>45483</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45226</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56324,7 +56324,7 @@
         <v>44818</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56397,7 +56397,7 @@
         <v>44988</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>46177</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>44875</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56616,7 +56616,7 @@
         <v>46030</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45112</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>44796</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>46219</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>45545</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>45070</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>46000</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>46230</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>46230</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>44956</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57366,7 +57366,7 @@
         <v>46273</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>45300</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>45282</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>46227</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45602</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>44901</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>45252</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>46275</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57960,7 +57960,7 @@
         <v>45082</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58033,7 +58033,7 @@
         <v>45673</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58106,7 +58106,7 @@
         <v>45668</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>44914</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>46280</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45257</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45688</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>46063</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58554,7 +58554,7 @@
         <v>45094</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58632,7 +58632,7 @@
         <v>44847</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58705,7 +58705,7 @@
         <v>45049</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58778,7 +58778,7 @@
         <v>45264</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58851,7 +58851,7 @@
         <v>45197</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>46287</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>46244</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59070,7 +59070,7 @@
         <v>45217</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>46204</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>44564</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>46287</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>44551</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>46287</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59523,7 +59523,7 @@
         <v>45561</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59596,7 +59596,7 @@
         <v>45063</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>46244</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>46288</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45748</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>46288</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45636</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>46246</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>45085</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>45701</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>45700</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>44855</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>44756</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>46247</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60570,7 +60570,7 @@
         <v>45022</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45463</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>45541</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>45541</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46252</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>46196</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
         <v>44587</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61101,7 +61101,7 @@
         <v>46190</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45327</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>46251</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>46162</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45769</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>46244</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61559,7 +61559,7 @@
         <v>46253</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61632,7 +61632,7 @@
         <v>46049</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>46000</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61778,7 +61778,7 @@
         <v>45590</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61851,7 +61851,7 @@
         <v>45984</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61929,7 +61929,7 @@
         <v>46058</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>46058</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62075,7 +62075,7 @@
         <v>46178</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62153,7 +62153,7 @@
         <v>46254</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62226,7 +62226,7 @@
         <v>46058</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62299,7 +62299,7 @@
         <v>46251</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62377,7 +62377,7 @@
         <v>46065</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62450,7 +62450,7 @@
         <v>46178</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>46244</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>46251</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>45984</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62762,7 +62762,7 @@
         <v>46204</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45672</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>45211</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62986,7 +62986,7 @@
         <v>46255</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>44566</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63132,7 +63132,7 @@
         <v>46132</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63210,7 +63210,7 @@
         <v>45153</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63283,7 +63283,7 @@
         <v>45926</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63361,7 +63361,7 @@
         <v>45022</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63439,7 +63439,7 @@
         <v>46204</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63512,7 +63512,7 @@
         <v>46258</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>45779</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63663,7 +63663,7 @@
         <v>46091</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63741,7 +63741,7 @@
         <v>45540</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63814,7 +63814,7 @@
         <v>46095</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63887,7 +63887,7 @@
         <v>46301</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>45205</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64033,7 +64033,7 @@
         <v>45622</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64106,7 +64106,7 @@
         <v>46095</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64179,7 +64179,7 @@
         <v>46115</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64252,7 +64252,7 @@
         <v>46126</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45679</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64398,7 +64398,7 @@
         <v>46178</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45555</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64549,7 +64549,7 @@
         <v>46128</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>45174</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64695,7 +64695,7 @@
         <v>44531</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64768,7 +64768,7 @@
         <v>46204</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64841,7 +64841,7 @@
         <v>45240</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>45178</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64992,7 +64992,7 @@
         <v>46255</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65070,7 +65070,7 @@
         <v>46255</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>46260</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65216,7 +65216,7 @@
         <v>46163</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65289,7 +65289,7 @@
         <v>45520</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65362,7 +65362,7 @@
         <v>46044</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65435,7 +65435,7 @@
         <v>46062</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65508,7 +65508,7 @@
         <v>46259</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         <v>46085</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65664,7 +65664,7 @@
         <v>45525</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65742,7 +65742,7 @@
         <v>46092</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>46307</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65888,7 +65888,7 @@
         <v>45404</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65961,7 +65961,7 @@
         <v>45188</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66034,7 +66034,7 @@
         <v>45475</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66107,7 +66107,7 @@
         <v>46262</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66185,7 +66185,7 @@
         <v>46262</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>46261</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66336,7 +66336,7 @@
         <v>46261</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>46261</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66487,7 +66487,7 @@
         <v>46262</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66565,7 +66565,7 @@
         <v>46261</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>46261</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66716,7 +66716,7 @@
         <v>45673</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66789,7 +66789,7 @@
         <v>45763</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66862,7 +66862,7 @@
         <v>45278</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66935,7 +66935,7 @@
         <v>46304</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67013,7 +67013,7 @@
         <v>46261</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67091,7 +67091,7 @@
         <v>46261</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67169,7 +67169,7 @@
         <v>46261</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67242,7 +67242,7 @@
         <v>45418</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67315,7 +67315,7 @@
         <v>46163</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67393,7 +67393,7 @@
         <v>46307</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67466,7 +67466,7 @@
         <v>46261</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67544,7 +67544,7 @@
         <v>46261</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>46261</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67700,7 +67700,7 @@
         <v>46262</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67778,7 +67778,7 @@
         <v>45614</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>46262</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67924,7 +67924,7 @@
         <v>46178</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68002,7 +68002,7 @@
         <v>46262</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68080,7 +68080,7 @@
         <v>46261</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68158,7 +68158,7 @@
         <v>46261</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68236,7 +68236,7 @@
         <v>45799</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68309,7 +68309,7 @@
         <v>45799</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68382,7 +68382,7 @@
         <v>45799</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68455,7 +68455,7 @@
         <v>46261</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68533,7 +68533,7 @@
         <v>46261</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68611,7 +68611,7 @@
         <v>46262</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68689,7 +68689,7 @@
         <v>45126</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68762,7 +68762,7 @@
         <v>46300</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68835,7 +68835,7 @@
         <v>45800</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68913,7 +68913,7 @@
         <v>45800</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68991,7 +68991,7 @@
         <v>45800</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69064,7 +69064,7 @@
         <v>45800</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69142,7 +69142,7 @@
         <v>45805</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69220,7 +69220,7 @@
         <v>46266</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69298,7 +69298,7 @@
         <v>46266</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69376,7 +69376,7 @@
         <v>45867</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69449,7 +69449,7 @@
         <v>45810</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69527,7 +69527,7 @@
         <v>46310</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69600,7 +69600,7 @@
         <v>46035</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69673,7 +69673,7 @@
         <v>46262</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69746,7 +69746,7 @@
         <v>45819</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69819,7 +69819,7 @@
         <v>46105</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69892,7 +69892,7 @@
         <v>45819</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69965,7 +69965,7 @@
         <v>45819</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70038,7 +70038,7 @@
         <v>45825</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70111,7 +70111,7 @@
         <v>45827</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70184,7 +70184,7 @@
         <v>45833</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70257,7 +70257,7 @@
         <v>45832</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70335,7 +70335,7 @@
         <v>45831</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70408,7 +70408,7 @@
         <v>45840</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70486,7 +70486,7 @@
         <v>45845</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70564,7 +70564,7 @@
         <v>45762</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70637,7 +70637,7 @@
         <v>45842</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70710,7 +70710,7 @@
         <v>45863</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70783,7 +70783,7 @@
         <v>45866</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70861,7 +70861,7 @@
         <v>45866</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70939,7 +70939,7 @@
         <v>45867</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71012,7 +71012,7 @@
         <v>44784</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71085,7 +71085,7 @@
         <v>45870</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71163,7 +71163,7 @@
         <v>45873</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71236,7 +71236,7 @@
         <v>45873</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71309,7 +71309,7 @@
         <v>45873</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71382,7 +71382,7 @@
         <v>45873</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71455,7 +71455,7 @@
         <v>45883</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71528,7 +71528,7 @@
         <v>45883</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71601,7 +71601,7 @@
         <v>45883</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71674,7 +71674,7 @@
         <v>44102</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71752,7 +71752,7 @@
         <v>45316</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71830,7 +71830,7 @@
         <v>45315</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71908,7 +71908,7 @@
         <v>45142</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71986,7 +71986,7 @@
         <v>44550</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72064,7 +72064,7 @@
         <v>45706</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72142,7 +72142,7 @@
         <v>45720</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72220,7 +72220,7 @@
         <v>45707</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72298,7 +72298,7 @@
         <v>45707</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72376,7 +72376,7 @@
         <v>46059</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72454,7 +72454,7 @@
         <v>46059</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72532,7 +72532,7 @@
         <v>46089</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72610,7 +72610,7 @@
         <v>46089</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45153</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>46181</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>46182</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>46086</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>46101</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45404</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45677</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44103</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>46125</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44505</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>46201</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>46216</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>46219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46219</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46053</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46091</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>46055</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45440</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>46185</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>46188</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>46201</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>46289</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>46251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>46253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46062</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45721</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>46031</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45187</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>44588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45699</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44505</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44515</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>44829</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45891</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>45891</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>46168</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>46169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>45930</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>46175</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44958</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>46182</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>46188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45089</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45981</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45453</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44955</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>46219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>46021</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>46281</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>46239</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>46239</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>46030</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45800</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45800</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>46059</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>46162</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>46069</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>46084</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>46254</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>46097</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>46105</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>46104</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45177</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>46301</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>46114</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>46304</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>46119</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>46303</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>46262</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>46262</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>46133</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45883</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>46269</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46045</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>46311</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46057</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45899</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>46148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45730</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44949</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>45446</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45252</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>45194</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44663</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45706</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45319</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45064</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45699</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45706</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44868</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44774</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44510</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44501</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44760</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44873</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44854</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44512</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>44635</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>44596</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44595</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44496</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>44501</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>44519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>44595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44861</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>44854</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>44523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44714</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44635</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44603</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45075</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45800</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44672</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45552</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45888</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45330</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45327</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45769</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45891</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44656</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45898</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45883</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45883</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45414</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45899</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45404</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45883</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45075</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45240</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45884</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45884</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45884</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45910</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45910</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44818</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46161</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46034</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46107</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46163</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>46030</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>46163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45916</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>46163</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46163</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>46163</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45103</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45919</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45730</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45730</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45919</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45320</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>46165</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>46165</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>46165</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46167</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45668</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>46168</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45268</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45063</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>46165</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45365</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45925</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45926</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46165</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45926</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46168</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45925</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>46169</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>46169</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>45930</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>46169</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>46169</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>46169</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>46052</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45252</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45931</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>46171</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>46171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45933</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46175</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46045</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45933</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45933</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45327</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45937</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45937</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45938</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45938</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>44949</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45939</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>46175</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46045</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45943</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>46177</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45930</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45930</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>46069</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>46177</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45945</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45480</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45288</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45946</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>46176</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46176</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45415</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45946</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45945</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45162</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45162</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>46178</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45327</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45576</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46178</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45087</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>46178</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>46183</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45512</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45169</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45957</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45212</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>46185</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>46185</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>46185</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>46185</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>46184</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>46184</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45541</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45467</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44797</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45265</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44988</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46101</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>45672</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45226</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>46191</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46034</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45968</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>46190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>45252</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45279</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45971</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46195</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45636</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45971</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45159</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>46196</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46196</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>46196</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>46196</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45567</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45069</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45978</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45975</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>46201</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45977</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45979</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46202</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45281</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46203</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>46204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45540</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>46204</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>44756</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45981</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45191</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>44914</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>46204</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45986</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>46205</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45985</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>46204</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>46204</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>44918</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45983</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>46205</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45984</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45984</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45984</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45667</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>46160</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>45722</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45992</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45992</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45992</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>46177</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45476</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45022</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>46030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45544</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45649</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45085</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>45999</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>46219</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>46000</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45986</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45999</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45999</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>46000</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45779</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>46000</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>46227</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45540</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>46230</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>46230</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44854</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45174</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45240</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45555</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45622</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45205</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>46063</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>46280</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45178</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44531</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>46013</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>45679</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45520</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>46021</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45525</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>46204</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46031</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>46031</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46034</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46035</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>46036</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46036</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>46036</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>46036</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>46036</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45475</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46035</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>46035</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>46038</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>46037</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>46042</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45188</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45404</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46287</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>46288</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>45418</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>46044</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>46043</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45278</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>46044</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>46043</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46287</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45614</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>46045</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45673</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46244</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45763</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45800</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45800</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45800</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>46244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>46045</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45799</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>46287</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45800</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>45799</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45799</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>46050</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>46051</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         <v>46247</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46246</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>46051</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>46050</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>46055</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>46055</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>46043</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>45805</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>46055</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>46056</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>46056</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45810</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45274</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>46062</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>46058</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>46058</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>46058</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>46062</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>46063</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>46063</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>46063</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>46063</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>46063</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>46190</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>46064</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>46063</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>46065</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>46066</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>46066</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>46066</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>46162</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>46065</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>46065</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>46069</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45483</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45300</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>46196</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>46069</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>46072</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>45819</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>46071</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>46251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>46072</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45819</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>46072</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46076</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45819</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>46031</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>46074</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46076</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>46253</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>46073</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45825</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>46034</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>46036</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>46078</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>46080</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45827</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>46252</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>46080</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>46085</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>46058</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>46084</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>46126</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>46084</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>46085</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>46085</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45832</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>46037</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46091</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>46095</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45831</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>46115</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>46084</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>46084</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>46178</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>46086</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>46087</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>46086</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46086</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46086</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>46058</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>46058</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45833</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>46087</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>46086</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46086</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46087</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>46251</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46086</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>46086</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>46086</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>46086</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46178</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>46128</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>46132</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>46095</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>46090</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>46000</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46043</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>46090</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>46091</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46244</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>46091</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>46092</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>46065</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>46093</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>46204</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>46092</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45984</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>46092</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>46093</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46092</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>46036</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>46094</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45840</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>46095</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>46095</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>46095</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>46097</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>46097</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>46094</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>46095</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45926</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>46097</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>46178</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>46254</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>46095</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>46255</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46255</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>45984</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>46098</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>46049</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>46099</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46099</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>46251</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>46099</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45842</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>46244</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>46099</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>46098</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>46100</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45845</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>46100</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>46101</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45762</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>46101</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>46044</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>46258</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>46301</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46746,7 +46746,7 @@
         <v>46105</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46819,7 +46819,7 @@
         <v>46107</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>46092</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>46107</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>46106</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>46204</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>46107</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>46111</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>46108</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>46111</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>46111</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>46108</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47657,7 +47657,7 @@
         <v>46204</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>46259</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>46112</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>46261</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>46261</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45866</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>46085</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45540</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>46115</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>46115</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45863</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>46115</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         <v>46261</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45866</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>46115</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>44845</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>46114</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>46115</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>46119</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>45867</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>46119</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>46116</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>46116</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49381,7 +49381,7 @@
         <v>46119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>46115</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>46261</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>46116</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46261</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>46119</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>46119</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>46119</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45870</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>46120</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>46121</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>44564</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>44784</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45873</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>46121</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>46163</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>46261</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>46261</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>46261</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>46261</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>46261</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>46260</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51047,7 +51047,7 @@
         <v>45873</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>46261</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>46261</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>45070</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51349,7 +51349,7 @@
         <v>46261</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45873</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>45873</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>46126</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>46126</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>46126</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>46099</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51865,7 +51865,7 @@
         <v>46062</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>46261</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>46261</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>46130</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>46132</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>46132</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52318,7 +52318,7 @@
         <v>46262</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>46262</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52469,7 +52469,7 @@
         <v>46129</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52547,7 +52547,7 @@
         <v>46128</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>46132</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>46128</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>46128</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>44994</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>44994</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46091</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>46132</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>46178</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>46091</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>46129</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>46129</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46129</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>46129</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46262</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>45069</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>46262</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46129</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>44972</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45721</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>46133</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>45884</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>46136</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46262</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>46091</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>46163</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54525,7 +54525,7 @@
         <v>46135</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54603,7 +54603,7 @@
         <v>44875</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54676,7 +54676,7 @@
         <v>46262</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54754,7 +54754,7 @@
         <v>46042</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>46262</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46307</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>46136</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>46307</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>46135</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>46086</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>46093</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>46065</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>46090</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45558</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>46310</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>46300</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45709</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>46266</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>44587</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>46048</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45356</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>46266</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45303</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56264,7 +56264,7 @@
         <v>46065</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56337,7 +56337,7 @@
         <v>46035</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56410,7 +56410,7 @@
         <v>46057</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45476</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>46063</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>45905</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56702,7 +56702,7 @@
         <v>46262</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56775,7 +56775,7 @@
         <v>46314</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>46055</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56921,7 +56921,7 @@
         <v>45735</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45779</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>46314</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>46314</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57213,7 +57213,7 @@
         <v>45099</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>46063</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57359,7 +57359,7 @@
         <v>46069</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>46314</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>46065</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>46063</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57651,7 +57651,7 @@
         <v>46071</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57724,7 +57724,7 @@
         <v>46052</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45238</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45562</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>46030</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58016,7 +58016,7 @@
         <v>45537</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>46104</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58162,7 +58162,7 @@
         <v>46038</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58235,7 +58235,7 @@
         <v>45595</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58308,7 +58308,7 @@
         <v>46061</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>45917</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>46046</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58527,7 +58527,7 @@
         <v>45728</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>46273</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>46140</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58746,7 +58746,7 @@
         <v>46058</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58819,7 +58819,7 @@
         <v>46085</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58892,7 +58892,7 @@
         <v>46080</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58965,7 +58965,7 @@
         <v>46036</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>45602</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>46069</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59184,7 +59184,7 @@
         <v>45883</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59262,7 +59262,7 @@
         <v>46048</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>46037</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>46029</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>46134</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>46105</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59632,7 +59632,7 @@
         <v>45252</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>46030</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45867</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>46071</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>46043</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>44994</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>46058</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>46105</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>46090</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46090</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>46141</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46072</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>46031</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45590</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>46038</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>45769</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>46275</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>45390</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>46065</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>46142</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>46148</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61175,7 +61175,7 @@
         <v>46147</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>46147</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>46147</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>46147</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>46147</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>46150</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>44956</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45217</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>45082</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>46043</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>46086</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>46048</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>46151</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>46086</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45094</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45182</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>46050</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>46079</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>46153</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>46035</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>44988</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>46108</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62826,7 +62826,7 @@
         <v>46094</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45261</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45261</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>46108</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45245</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>45478</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>46104</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>44797</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>45022</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63483,7 +63483,7 @@
         <v>45671</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63556,7 +63556,7 @@
         <v>45589</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>45602</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>45615</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         <v>44582</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>45693</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>45730</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45649</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45649</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>45226</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45188</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>45670</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>44843</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64457,7 +64457,7 @@
         <v>45706</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>45191</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64603,7 +64603,7 @@
         <v>45771</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>45211</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64749,7 +64749,7 @@
         <v>45700</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>45257</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>45523</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64978,7 +64978,7 @@
         <v>45755</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65051,7 +65051,7 @@
         <v>45210</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65124,7 +65124,7 @@
         <v>44908</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>45636</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>45721</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65348,7 +65348,7 @@
         <v>45721</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65426,7 +65426,7 @@
         <v>44847</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65499,7 +65499,7 @@
         <v>45649</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>44901</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65645,7 +65645,7 @@
         <v>45561</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65718,7 +65718,7 @@
         <v>45049</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>44501</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>45721</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65942,7 +65942,7 @@
         <v>45121</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66015,7 +66015,7 @@
         <v>44918</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>45701</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66161,7 +66161,7 @@
         <v>44551</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>44510</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66312,7 +66312,7 @@
         <v>45545</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66390,7 +66390,7 @@
         <v>45483</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66463,7 +66463,7 @@
         <v>45343</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66536,7 +66536,7 @@
         <v>44988</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66609,7 +66609,7 @@
         <v>45112</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66682,7 +66682,7 @@
         <v>45161</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66755,7 +66755,7 @@
         <v>45615</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66828,7 +66828,7 @@
         <v>45666</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66901,7 +66901,7 @@
         <v>45748</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66974,7 +66974,7 @@
         <v>44855</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67052,7 +67052,7 @@
         <v>45162</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67125,7 +67125,7 @@
         <v>45112</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67198,7 +67198,7 @@
         <v>44586</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>45120</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67344,7 +67344,7 @@
         <v>45191</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67422,7 +67422,7 @@
         <v>45639</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67495,7 +67495,7 @@
         <v>44549</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67568,7 +67568,7 @@
         <v>44813</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67641,7 +67641,7 @@
         <v>45541</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67719,7 +67719,7 @@
         <v>45701</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67792,7 +67792,7 @@
         <v>44566</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67865,7 +67865,7 @@
         <v>45075</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67943,7 +67943,7 @@
         <v>45153</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68016,7 +68016,7 @@
         <v>45153</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68089,7 +68089,7 @@
         <v>45112</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68162,7 +68162,7 @@
         <v>45638</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68235,7 +68235,7 @@
         <v>45673</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68308,7 +68308,7 @@
         <v>44810</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68381,7 +68381,7 @@
         <v>45212</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68459,7 +68459,7 @@
         <v>45205</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68532,7 +68532,7 @@
         <v>45208</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68605,7 +68605,7 @@
         <v>45211</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68678,7 +68678,7 @@
         <v>45666</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68751,7 +68751,7 @@
         <v>45698</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68824,7 +68824,7 @@
         <v>45209</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68902,7 +68902,7 @@
         <v>45240</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68975,7 +68975,7 @@
         <v>45645</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69053,7 +69053,7 @@
         <v>45701</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69126,7 +69126,7 @@
         <v>45701</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69199,7 +69199,7 @@
         <v>45615</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69272,7 +69272,7 @@
         <v>45688</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69345,7 +69345,7 @@
         <v>45769</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69418,7 +69418,7 @@
         <v>45250</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69491,7 +69491,7 @@
         <v>45251</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69564,7 +69564,7 @@
         <v>45463</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69637,7 +69637,7 @@
         <v>45226</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69710,7 +69710,7 @@
         <v>44804</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69783,7 +69783,7 @@
         <v>45408</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69861,7 +69861,7 @@
         <v>44744</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69934,7 +69934,7 @@
         <v>45246</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70007,7 +70007,7 @@
         <v>45321</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70080,7 +70080,7 @@
         <v>45530</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70153,7 +70153,7 @@
         <v>45196</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70226,7 +70226,7 @@
         <v>44796</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70304,7 +70304,7 @@
         <v>44846</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70377,7 +70377,7 @@
         <v>45153</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70450,7 +70450,7 @@
         <v>45488</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70523,7 +70523,7 @@
         <v>44586</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70596,7 +70596,7 @@
         <v>45282</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70669,7 +70669,7 @@
         <v>45264</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70742,7 +70742,7 @@
         <v>45265</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70815,7 +70815,7 @@
         <v>45293</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70888,7 +70888,7 @@
         <v>45293</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70961,7 +70961,7 @@
         <v>45660</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71034,7 +71034,7 @@
         <v>45540</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71107,7 +71107,7 @@
         <v>45260</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71180,7 +71180,7 @@
         <v>44544</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71253,7 +71253,7 @@
         <v>44988</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71326,7 +71326,7 @@
         <v>44988</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71399,7 +71399,7 @@
         <v>45022</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71477,7 +71477,7 @@
         <v>45374</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71550,7 +71550,7 @@
         <v>45376</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71623,7 +71623,7 @@
         <v>45562</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71696,7 +71696,7 @@
         <v>45271</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71774,7 +71774,7 @@
         <v>45070</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71847,7 +71847,7 @@
         <v>44102</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71925,7 +71925,7 @@
         <v>44550</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72003,7 +72003,7 @@
         <v>45316</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72081,7 +72081,7 @@
         <v>45315</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72159,7 +72159,7 @@
         <v>45706</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72237,7 +72237,7 @@
         <v>45142</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72315,7 +72315,7 @@
         <v>45720</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72393,7 +72393,7 @@
         <v>45707</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72471,7 +72471,7 @@
         <v>45707</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72549,7 +72549,7 @@
         <v>46059</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72627,7 +72627,7 @@
         <v>46059</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72705,7 +72705,7 @@
         <v>46089</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72783,7 +72783,7 @@
         <v>46089</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>

--- a/Översikt SANDVIKEN.xlsx
+++ b/Översikt SANDVIKEN.xlsx
@@ -601,7 +601,7 @@
         <v>44679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>46056</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45075</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45701</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45153</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>46181</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>46182</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>46086</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>46101</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45404</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45677</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44103</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>46125</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44505</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>46201</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>46216</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>46219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46219</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46053</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46091</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>46055</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45319</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45440</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>46185</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>46188</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>46201</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>46289</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>46251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>46253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46062</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45721</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>46031</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45187</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>44588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45699</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44505</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44515</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>44829</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45891</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>45891</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>46168</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>46169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>45930</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>46175</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44958</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>46182</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>46188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45089</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45981</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45453</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44955</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>46219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>46021</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>46281</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>46239</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>46239</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>46030</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45800</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45800</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>46059</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>46162</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>46069</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>46084</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>46254</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>46097</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>46105</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>46104</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45177</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>46301</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>46114</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>46304</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>46119</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>46303</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>46262</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>46262</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>46133</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45883</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>46269</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46045</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>46311</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46057</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45899</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>46148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45730</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44949</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>45446</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45252</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>45194</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44663</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45706</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45319</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45064</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45699</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45706</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44868</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44774</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44510</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44501</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44760</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44873</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44854</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44512</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>44635</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>44596</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44595</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44496</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>44501</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>44519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>44595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44861</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>44854</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>44523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44714</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44635</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44603</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45075</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45800</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44672</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45552</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45888</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45330</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45327</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45769</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45891</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44656</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45898</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45883</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45883</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45414</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45899</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45404</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45883</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45075</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45240</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45884</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45884</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45884</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45910</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45910</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44818</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46161</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46034</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46107</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46163</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>46030</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>46163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45916</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>46163</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46163</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>46163</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45103</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45919</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45730</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45730</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45919</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45320</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>46165</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>46165</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>46165</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46167</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45668</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>46168</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45268</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45063</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>46165</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45365</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45925</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45926</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46165</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45926</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46168</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45925</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>46169</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>46169</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>45930</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>46169</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>46169</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>46169</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>46052</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45252</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45931</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>46171</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>46171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45933</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46175</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46045</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45933</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45933</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45327</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45937</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45937</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45938</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45938</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>44949</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45939</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>46175</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46045</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45943</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>46177</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45930</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45930</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>46069</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>46177</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45945</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45480</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45288</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45946</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>46176</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46176</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45415</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45946</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45945</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45162</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45162</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>46178</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45327</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45576</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46178</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45087</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>46178</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>46183</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45512</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45169</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45957</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45212</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>46185</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>46185</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>46185</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>46185</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>46184</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>46184</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45541</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45467</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44797</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45265</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44988</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46101</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>45672</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45226</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>46191</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46034</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45968</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>46190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>45252</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45279</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45971</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46195</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45636</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45971</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45159</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>46196</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46196</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>46196</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>46196</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45567</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45069</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45978</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45975</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>46201</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45977</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45979</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46202</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45281</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46203</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>46204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45540</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>46204</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>44756</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45981</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45191</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>44914</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>46204</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45986</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>46205</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45985</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>46204</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>46204</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>44918</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45983</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>46205</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45984</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45984</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45984</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45667</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>46160</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>45722</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45992</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45992</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45992</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>46177</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45476</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45022</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>46030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45544</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45649</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45085</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>45999</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>46219</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>46000</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45986</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45999</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45999</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>46000</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45779</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>46000</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>46227</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45540</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>46230</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>46230</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44854</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45174</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45240</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45555</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45622</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45205</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>46063</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>46280</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45178</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44531</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>46013</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>45679</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45520</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>46021</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45525</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>46204</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46031</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>46031</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46034</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46035</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>46036</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46036</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>46036</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>46036</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>46036</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45475</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46035</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>46035</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>46038</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>46037</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>46042</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45188</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45404</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46287</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>46288</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>45418</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>46044</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>46043</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45278</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>46044</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>46043</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46287</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45614</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>46045</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45673</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46244</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45763</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45800</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45800</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45800</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>46244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>46045</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45799</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>46287</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45800</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>45799</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45799</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>46050</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>46051</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         <v>46247</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46246</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>46051</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>46050</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>46055</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>46055</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>46043</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>45805</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>46055</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>46056</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>46056</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45810</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45274</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>46062</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>46058</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>46058</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>46058</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>46062</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>46063</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>46063</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>46063</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>46063</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>46063</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>46190</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>46064</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>46063</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>46065</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>46066</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>46066</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>46066</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>46162</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>46065</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>46065</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>46069</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45483</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45300</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>46196</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>46069</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>46072</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>45819</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>46071</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>46251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>46072</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45819</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>46072</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46076</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45819</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>46031</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>46074</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46076</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>46253</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>46073</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45825</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>46034</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>46036</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>46078</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>46080</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45827</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>46252</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>46080</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>46085</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>46058</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>46084</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>46126</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>46084</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>46085</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>46085</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45832</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>46037</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46091</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>46095</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45831</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>46115</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>46084</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>46084</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>46178</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>46086</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>46087</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>46086</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46086</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46086</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>46058</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>46058</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45833</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>46087</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>46086</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46086</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46087</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>46251</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46086</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>46086</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>46086</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>46086</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46178</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>46128</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>46132</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>46095</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>46090</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>46000</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46043</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>46090</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>46091</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46244</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>46091</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>46092</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>46065</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>46093</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>46204</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>46092</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45984</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>46092</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>46093</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46092</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>46036</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>46094</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45840</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>46095</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>46095</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>46095</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>46097</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>46097</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>46094</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>46095</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45926</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>46097</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>46178</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>46254</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>46095</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>46255</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46255</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>45984</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>46098</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>46049</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>46099</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46099</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>46251</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>46099</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45842</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>46244</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>46099</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>46098</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>46100</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45845</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>46100</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>46101</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45762</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>46101</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>46044</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>46258</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>46301</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46746,7 +46746,7 @@
         <v>46105</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46819,7 +46819,7 @@
         <v>46107</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>46092</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>46107</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>46106</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>46204</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>46107</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>46111</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>46108</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>46111</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>46111</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>46108</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47657,7 +47657,7 @@
         <v>46204</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>46259</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>46112</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>46261</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>46261</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45866</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>46085</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45540</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>46115</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>46115</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45863</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>46115</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         <v>46261</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45866</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>46115</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>44845</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>46114</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>46115</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>46119</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>45867</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>46119</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>46116</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>46116</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49381,7 +49381,7 @@
         <v>46119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>46115</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>46261</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>46116</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46261</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>46119</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>46119</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>46119</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45870</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>46120</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>46121</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>44564</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>44784</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45873</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>46121</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>46163</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>46261</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>46261</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>46261</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>46261</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>46261</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>46260</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51047,7 +51047,7 @@
         <v>45873</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>46261</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>46261</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>45070</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51349,7 +51349,7 @@
         <v>46261</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45873</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>45873</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>46126</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>46126</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>46126</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>46099</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51865,7 +51865,7 @@
         <v>46062</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>46261</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>46261</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>46130</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>46132</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>46132</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52318,7 +52318,7 @@
         <v>46262</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>46262</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52469,7 +52469,7 @@
         <v>46129</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52547,7 +52547,7 @@
         <v>46128</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>46132</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>46128</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>46128</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>44994</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>44994</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46091</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>46132</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>46178</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>46091</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>46129</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>46129</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46129</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>46129</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46262</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>45069</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>46262</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46129</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>44972</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45721</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>46133</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>45884</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>46136</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46262</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>46091</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>46163</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54525,7 +54525,7 @@
         <v>46135</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54603,7 +54603,7 @@
         <v>44875</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54676,7 +54676,7 @@
         <v>46262</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54754,7 +54754,7 @@
         <v>46042</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>46262</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46307</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>46136</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>46307</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>46135</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>46086</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>46093</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>46065</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>46090</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45558</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>46310</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>46300</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45709</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>46266</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>44587</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>46048</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45356</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>46266</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45303</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56264,7 +56264,7 @@
         <v>46065</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56337,7 +56337,7 @@
         <v>46035</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56410,7 +56410,7 @@
         <v>46057</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45476</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>46063</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>45905</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56702,7 +56702,7 @@
         <v>46262</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56775,7 +56775,7 @@
         <v>46314</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>46055</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56921,7 +56921,7 @@
         <v>45735</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45779</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>46314</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>46314</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57213,7 +57213,7 @@
         <v>45099</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>46063</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57359,7 +57359,7 @@
         <v>46069</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>46314</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>46065</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>46063</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57651,7 +57651,7 @@
         <v>46071</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57724,7 +57724,7 @@
         <v>46052</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45238</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45562</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>46030</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58016,7 +58016,7 @@
         <v>45537</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>46104</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58162,7 +58162,7 @@
         <v>46038</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58235,7 +58235,7 @@
         <v>45595</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58308,7 +58308,7 @@
         <v>46061</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>45917</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>46046</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58527,7 +58527,7 @@
         <v>45728</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>46273</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>46140</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58746,7 +58746,7 @@
         <v>46058</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58819,7 +58819,7 @@
         <v>46085</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58892,7 +58892,7 @@
         <v>46080</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58965,7 +58965,7 @@
         <v>46036</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>45602</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>46069</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59184,7 +59184,7 @@
         <v>45883</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59262,7 +59262,7 @@
         <v>46048</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>46037</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>46029</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>46134</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>46105</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59632,7 +59632,7 @@
         <v>45252</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>46030</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45867</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>46071</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>46043</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>44994</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>46058</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>46105</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>46090</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46090</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>46141</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46072</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>46031</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45590</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>46038</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>45769</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>46275</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>45390</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>46065</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>46142</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>46148</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61175,7 +61175,7 @@
         <v>46147</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>46147</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>46147</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>46147</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>46147</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>46150</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>44956</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45217</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>45082</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>46043</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>46086</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>46048</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>46151</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>46086</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45094</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45182</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>46050</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>46079</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>46153</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>46035</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>44988</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>46108</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62826,7 +62826,7 @@
         <v>46094</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45261</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45261</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>46108</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45245</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>45478</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>46104</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>44797</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>45022</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63483,7 +63483,7 @@
         <v>45671</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63556,7 +63556,7 @@
         <v>45589</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>45602</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>45615</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         <v>44582</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>45693</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>45730</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45649</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45649</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>45226</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45188</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>45670</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>44843</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64457,7 +64457,7 @@
         <v>45706</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>45191</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64603,7 +64603,7 @@
         <v>45771</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>45211</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64749,7 +64749,7 @@
         <v>45700</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>45257</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>45523</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64978,7 +64978,7 @@
         <v>45755</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65051,7 +65051,7 @@
         <v>45210</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65124,7 +65124,7 @@
         <v>44908</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>45636</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>45721</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65348,7 +65348,7 @@
         <v>45721</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65426,7 +65426,7 @@
         <v>44847</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65499,7 +65499,7 @@
         <v>45649</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>44901</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65645,7 +65645,7 @@
         <v>45561</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65718,7 +65718,7 @@
         <v>45049</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>44501</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>45721</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65942,7 +65942,7 @@
         <v>45121</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66015,7 +66015,7 @@
         <v>44918</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>45701</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66161,7 +66161,7 @@
         <v>44551</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>44510</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66312,7 +66312,7 @@
         <v>45545</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66390,7 +66390,7 @@
         <v>45483</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66463,7 +66463,7 @@
         <v>45343</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66536,7 +66536,7 @@
         <v>44988</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66609,7 +66609,7 @@
         <v>45112</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66682,7 +66682,7 @@
         <v>45161</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66755,7 +66755,7 @@
         <v>45615</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66828,7 +66828,7 @@
         <v>45666</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66901,7 +66901,7 @@
         <v>45748</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66974,7 +66974,7 @@
         <v>44855</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67052,7 +67052,7 @@
         <v>45162</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67125,7 +67125,7 @@
         <v>45112</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67198,7 +67198,7 @@
         <v>44586</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>45120</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67344,7 +67344,7 @@
         <v>45191</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67422,7 +67422,7 @@
         <v>45639</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67495,7 +67495,7 @@
         <v>44549</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67568,7 +67568,7 @@
         <v>44813</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67641,7 +67641,7 @@
         <v>45541</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67719,7 +67719,7 @@
         <v>45701</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67792,7 +67792,7 @@
         <v>44566</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67865,7 +67865,7 @@
         <v>45075</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67943,7 +67943,7 @@
         <v>45153</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68016,7 +68016,7 @@
         <v>45153</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68089,7 +68089,7 @@
         <v>45112</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68162,7 +68162,7 @@
         <v>45638</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68235,7 +68235,7 @@
         <v>45673</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68308,7 +68308,7 @@
         <v>44810</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68381,7 +68381,7 @@
         <v>45212</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68459,7 +68459,7 @@
         <v>45205</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68532,7 +68532,7 @@
         <v>45208</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68605,7 +68605,7 @@
         <v>45211</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68678,7 +68678,7 @@
         <v>45666</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68751,7 +68751,7 @@
         <v>45698</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68824,7 +68824,7 @@
         <v>45209</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68902,7 +68902,7 @@
         <v>45240</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68975,7 +68975,7 @@
         <v>45645</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69053,7 +69053,7 @@
         <v>45701</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69126,7 +69126,7 @@
         <v>45701</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69199,7 +69199,7 @@
         <v>45615</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69272,7 +69272,7 @@
         <v>45688</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69345,7 +69345,7 @@
         <v>45769</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69418,7 +69418,7 @@
         <v>45250</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69491,7 +69491,7 @@
         <v>45251</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69564,7 +69564,7 @@
         <v>45463</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69637,7 +69637,7 @@
         <v>45226</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69710,7 +69710,7 @@
         <v>44804</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69783,7 +69783,7 @@
         <v>45408</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69861,7 +69861,7 @@
         <v>44744</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69934,7 +69934,7 @@
         <v>45246</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70007,7 +70007,7 @@
         <v>45321</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70080,7 +70080,7 @@
         <v>45530</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70153,7 +70153,7 @@
         <v>45196</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70226,7 +70226,7 @@
         <v>44796</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70304,7 +70304,7 @@
         <v>44846</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70377,7 +70377,7 @@
         <v>45153</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70450,7 +70450,7 @@
         <v>45488</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70523,7 +70523,7 @@
         <v>44586</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70596,7 +70596,7 @@
         <v>45282</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70669,7 +70669,7 @@
         <v>45264</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70742,7 +70742,7 @@
         <v>45265</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70815,7 +70815,7 @@
         <v>45293</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70888,7 +70888,7 @@
         <v>45293</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70961,7 +70961,7 @@
         <v>45660</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71034,7 +71034,7 @@
         <v>45540</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71107,7 +71107,7 @@
         <v>45260</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71180,7 +71180,7 @@
         <v>44544</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71253,7 +71253,7 @@
         <v>44988</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71326,7 +71326,7 @@
         <v>44988</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71399,7 +71399,7 @@
         <v>45022</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71477,7 +71477,7 @@
         <v>45374</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71550,7 +71550,7 @@
         <v>45376</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71623,7 +71623,7 @@
         <v>45562</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71696,7 +71696,7 @@
         <v>45271</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71774,7 +71774,7 @@
         <v>45070</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71847,7 +71847,7 @@
         <v>44102</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71925,7 +71925,7 @@
         <v>44550</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72003,7 +72003,7 @@
         <v>45316</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72081,7 +72081,7 @@
         <v>45315</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72159,7 +72159,7 @@
         <v>45706</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72237,7 +72237,7 @@
         <v>45142</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72315,7 +72315,7 @@
         <v>45720</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -72393,7 +72393,7 @@
         <v>45707</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -72471,7 +72471,7 @@
         <v>45707</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72549,7 +72549,7 @@
         <v>46059</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72627,7 +72627,7 @@
         <v>46059</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72705,7 +72705,7 @@
         <v>46089</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72783,7 +72783,7 @@
         <v>46089</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
